--- a/excel_test_cases_updated/test_create_pr_copy.xlsx
+++ b/excel_test_cases_updated/test_create_pr_copy.xlsx
@@ -1,180 +1,881 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samit paudel\Downloads\ariba_automation\sap_test_automation\excel_test_cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="878" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="878" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario Cover Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Steps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="References" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Scenario Metrics " sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Scenario Cover Sheet" sheetId="15" r:id="rId1"/>
+    <sheet name="Steps" sheetId="17" r:id="rId2"/>
+    <sheet name="References" sheetId="18" r:id="rId3"/>
+    <sheet name="Scenario Metrics " sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Steps!$A$1:$Q$14</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
+  <si>
+    <t xml:space="preserve">Scenario Owner: </t>
+  </si>
+  <si>
+    <t>Test Cycle:</t>
+  </si>
+  <si>
+    <t>Scenario ID:</t>
+  </si>
+  <si>
+    <t>GPO-001</t>
+  </si>
+  <si>
+    <t>Test Objective:</t>
+  </si>
+  <si>
+    <t>Create PR and PO in guided buying.</t>
+  </si>
+  <si>
+    <t>Scenario Description:</t>
+  </si>
+  <si>
+    <t>Long Description Scenario Summary for items to be tested</t>
+  </si>
+  <si>
+    <t>Search catalog for items
+Add items to cart
+Complete requisition details and submit
+Review PR approval flow 
+Confirm PO generation
+Create associated receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Data Requirements</t>
+  </si>
+  <si>
+    <t>Legacy Reference</t>
+  </si>
+  <si>
+    <t>SAP Reference</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prerequisite </t>
+  </si>
+  <si>
+    <t>Key RICEF Objects</t>
+  </si>
+  <si>
+    <t>Master Data Validation</t>
+  </si>
+  <si>
+    <t>SAP PO Post and Validation</t>
+  </si>
+  <si>
+    <t>SAP Invoice to SAP</t>
+  </si>
+  <si>
+    <t>Payment Remitance Validation to Ariba</t>
+  </si>
+  <si>
+    <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Scenario Number</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description </t>
+  </si>
+  <si>
+    <t>Test Data / Test Execution</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Step Completed
+Sucessfullyåç</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>FI Impact</t>
+  </si>
+  <si>
+    <t>RICEF Tested</t>
+  </si>
+  <si>
+    <t>TPR #</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Tester/User ID</t>
+  </si>
+  <si>
+    <t>Y or N</t>
+  </si>
+  <si>
+    <t>Scenario No.</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>BL_001</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Buyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login
+Password
+</t>
+  </si>
+  <si>
+    <t>Catalog</t>
+  </si>
+  <si>
+    <t>Desired quantity is indicated.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Press</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add to Cart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" button.</t>
+    </r>
+  </si>
+  <si>
+    <t>Shopping Cart popup  window appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>Requisition screen appears. The system assigns the PR number to the document.</t>
+  </si>
+  <si>
+    <t>Requisition Header</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enter the requistion title on "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Requistion title</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" box.</t>
+    </r>
+  </si>
+  <si>
+    <t>Requisition title is updated.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enter or verify the remaing data elements on the Requistion screen.
+Note: Only "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">red </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" items should be editable.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Fields are updated without any error.</t>
+  </si>
+  <si>
+    <t>Need-by is Today +5</t>
+  </si>
+  <si>
+    <t>Requisition Lines</t>
+  </si>
+  <si>
+    <t>Fields are updated</t>
+  </si>
+  <si>
+    <t>Requisition</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Press "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"  to submit the requisition for approval. </t>
+    </r>
+  </si>
+  <si>
+    <t>Message appears "Your requisition has been sent for approval.</t>
+  </si>
+  <si>
+    <t>View Approval Flow</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Click on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Requisition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to display the created requisiton. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Submitted</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The PR is now on Submitted status.
+Approval Flow is now active shown by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>green flow.</t>
+    </r>
+  </si>
+  <si>
+    <t>Count of Status</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>10 - Not Started</t>
+  </si>
+  <si>
+    <t>20 - In-Process</t>
+  </si>
+  <si>
+    <t>30 - TPR Hold</t>
+  </si>
+  <si>
+    <t>40 - DEV Hold</t>
+  </si>
+  <si>
+    <t>50 - Pass</t>
+  </si>
+  <si>
+    <t>60 - N/A</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>PP_018</t>
+  </si>
+  <si>
+    <t>RTR</t>
+  </si>
+  <si>
+    <t>PTP</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>IMWM</t>
+  </si>
+  <si>
+    <t>PP_018 Total</t>
+  </si>
+  <si>
+    <t>ZZZ999</t>
+  </si>
+  <si>
+    <t>ZZZ999 Total</t>
+  </si>
+  <si>
+    <t>Complete script GEN-002 to log into Ariba "Advanced" Buying and Invoicing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexus Water Group homepage is presented. </t>
+  </si>
+  <si>
+    <t>Click on Catalog Tab</t>
+  </si>
+  <si>
+    <t>Catalog page is displayed</t>
+  </si>
+  <si>
+    <t>On the search bar where it says "Search by part #, supplier name or keyword", type in the item you want to purchase.</t>
+  </si>
+  <si>
+    <t>Book Bins - Set of 12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From the search result, find the item. Enter the desired quantity  in the "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> box.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen. Click on Proceed to Checkout button.
+</t>
+  </si>
+  <si>
+    <t>AT-1</t>
+  </si>
+  <si>
+    <r>
+      <t>Click on the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkbox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the line for the item (towards the item lines' top left).
+Click on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dropdown and then </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Edit Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Edit Detail page for the item is displayed.</t>
+  </si>
+  <si>
+    <r>
+      <t>Scroll down to Accounting - by Line Item Section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter or  verify the information in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accounting  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">section. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Enter or  verify the information in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Shipping - by Line Item </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>section.</t>
+    </r>
+  </si>
+  <si>
+    <t>Enter or verify the Line Item Details for the item.
+(Most details in this section is set to default)</t>
+  </si>
+  <si>
+    <t>Fields are validated and updated if necessary.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="8"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="12"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <i val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
-      <color rgb="FF00B050"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF262626"/>
       <name val="Calibri"/>
-      <color rgb="FF262626"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF00B050"/>
-      <sz val="16"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -216,7 +917,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -796,413 +1497,316 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="123">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="1" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="1" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1392,58 +1996,58 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
@@ -1496,22 +2100,56 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00B0F0"/>
+      <color rgb="FFE2EFDA"/>
+      <color rgb="FFCEE4CB"/>
+      <color rgb="FFFDE9D9"/>
+      <color rgb="FFE4DFEC"/>
+      <color rgb="FFDDEBF7"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" refreshedBy="Browning G Hollomon" refreshedDate="39386.43617974537" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1" r:id="rId1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Browning G Hollomon" refreshedDate="39386.436179745368" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final"/>
+    <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final" r:id="rId2"/>
   </cacheSource>
   <cacheFields count="15">
-    <cacheField name="Scenario Number" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="28" containsBlank="1">
+    <cacheField name="Scenario Number" numFmtId="0">
+      <sharedItems containsBlank="1" count="28">
         <m/>
         <s v="Demand Planning"/>
         <s v="FTS001"/>
@@ -1542,11 +2180,11 @@
         <s v="OTC001" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Step" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsInteger="1" containsNumber="1" containsString="0" minValue="1" maxValue="46"/>
+    <cacheField name="Step" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="46"/>
     </cacheField>
-    <cacheField name="Team" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="7" containsBlank="1">
+    <cacheField name="Team" numFmtId="0">
+      <sharedItems containsBlank="1" count="7">
         <m/>
         <s v="FTS"/>
         <s v="PTP"/>
@@ -1556,35 +2194,35 @@
         <s v="XXX" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Description " uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Description " numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tcode" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Tcode" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tester" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Tester" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Test Data / Test Execution" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Test Data / Test Execution" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Expected Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Expected Result" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Actual Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Actual Result" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="FI Impact" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="FI Impact" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="RICEF Tested" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="RICEF Tested" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="TPR #" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="TPR #" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Status" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="34" containsBlank="1">
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems containsBlank="1" count="34">
         <m/>
         <s v="50 - Pass"/>
         <s v="60 - N/A"/>
@@ -1621,18 +2259,23 @@
         <s v="20 In Process" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="User ID" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="User ID" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Comments" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="Comments" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="137">
   <r>
     <x v="0"/>
     <m/>
@@ -3966,231 +4609,231 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" dataCaption="Data" showError="0" showMissing="1" updatedVersion="3" minRefreshableVersion="0" asteriskTotals="0" showItems="1" editData="0" disableFieldList="0" showCalcMbrs="1" visualTotals="1" showMultipleLabel="1" showDataDropDown="1" showDrill="1" printDrill="0" showMemberPropertyTips="0" showDataTips="1" enableWizard="1" enableDrill="1" enableFieldProperties="1" preserveFormatting="1" useAutoFormatting="1" pageWrap="0" pageOverThenDown="0" subtotalHiddenItems="0" rowGrandTotals="1" colGrandTotals="1" fieldPrintTitles="0" itemPrintTitles="1" mergeItem="0" showDropZones="1" createdVersion="1" indent="0" showEmptyRow="0" showEmptyCol="0" showHeaders="1" compact="0" outline="0" outlineData="0" compactData="0" published="0" gridDropZones="1" immersive="1" multipleFieldFilters="0" chartFormat="0" fieldListSortAscending="0" mdxSubqueries="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" r:id="rId1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:J12" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="15">
-    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="29">
-        <item t="data" h="1" sd="1" m="1" x="27"/>
-        <item t="data" h="1" sd="1" x="0"/>
-        <item t="data" h="1" sd="1" m="1" x="10"/>
-        <item n="PP_018" t="data" sd="1" x="2"/>
-        <item t="data" sd="1" m="1" x="8"/>
-        <item t="data" sd="1" x="7"/>
-        <item t="data" sd="1" m="1" x="16"/>
-        <item t="data" sd="1" m="1" x="18"/>
-        <item t="data" sd="1" m="1" x="20"/>
-        <item t="data" sd="1" m="1" x="22"/>
-        <item t="data" sd="1" m="1" x="23"/>
-        <item t="data" sd="1" m="1" x="24"/>
-        <item t="data" sd="1" m="1" x="25"/>
-        <item t="data" sd="1" m="1" x="26"/>
-        <item t="data" sd="1" m="1" x="9"/>
-        <item t="data" sd="1" m="1" x="11"/>
-        <item t="data" sd="1" m="1" x="12"/>
-        <item t="data" sd="1" m="1" x="13"/>
-        <item t="data" sd="1" m="1" x="14"/>
-        <item t="data" sd="1" m="1" x="15"/>
-        <item t="data" sd="1" m="1" x="17"/>
-        <item t="data" sd="1" m="1" x="19"/>
-        <item t="data" sd="1" m="1" x="21"/>
-        <item t="data" sd="1" x="1"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="5"/>
-        <item t="data" sd="1" x="6"/>
-        <item t="default" sd="1"/>
+        <item h="1" m="1" x="27"/>
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="10"/>
+        <item n="PP_018" x="2"/>
+        <item m="1" x="8"/>
+        <item x="7"/>
+        <item m="1" x="16"/>
+        <item m="1" x="18"/>
+        <item m="1" x="20"/>
+        <item m="1" x="22"/>
+        <item m="1" x="23"/>
+        <item m="1" x="24"/>
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="9"/>
+        <item m="1" x="11"/>
+        <item m="1" x="12"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
+        <item m="1" x="17"/>
+        <item m="1" x="19"/>
+        <item m="1" x="21"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="8">
-        <item t="data" h="1" sd="1" x="0"/>
-        <item t="data" sd="1" m="1" x="5"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="2"/>
-        <item n="PP" t="data" sd="1" x="1"/>
-        <item t="data" sd="1" m="1" x="6"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="default" sd="1"/>
+        <item h="1" x="0"/>
+        <item m="1" x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item n="PP" x="1"/>
+        <item m="1" x="6"/>
+        <item x="3"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField axis="axisCol" dataField="1" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisCol" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="35">
-        <item t="data" sd="1" m="1" x="12"/>
-        <item t="data" sd="1" m="1" x="16"/>
-        <item t="data" sd="1" m="1" x="29"/>
-        <item t="data" sd="1" m="1" x="31"/>
-        <item t="data" sd="1" m="1" x="24"/>
-        <item t="data" sd="1" x="0"/>
-        <item t="data" sd="1" m="1" x="17"/>
-        <item t="data" sd="1" m="1" x="33"/>
-        <item t="data" sd="1" m="1" x="26"/>
-        <item t="data" sd="1" m="1" x="13"/>
-        <item t="data" sd="1" m="1" x="9"/>
-        <item t="data" sd="1" m="1" x="25"/>
-        <item t="data" sd="1" m="1" x="8"/>
-        <item t="data" sd="1" m="1" x="28"/>
-        <item t="data" sd="1" m="1" x="19"/>
-        <item t="data" sd="1" m="1" x="30"/>
-        <item t="data" sd="1" m="1" x="15"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="5"/>
-        <item t="data" sd="1" x="6"/>
-        <item t="data" sd="1" m="1" x="10"/>
-        <item t="data" sd="1" m="1" x="18"/>
-        <item t="data" sd="1" m="1" x="11"/>
-        <item t="data" sd="1" m="1" x="22"/>
-        <item t="data" sd="1" m="1" x="32"/>
-        <item t="data" sd="1" m="1" x="20"/>
-        <item t="data" sd="1" m="1" x="27"/>
-        <item t="data" sd="1" m="1" x="14"/>
-        <item t="data" sd="1" m="1" x="23"/>
-        <item t="data" sd="1" m="1" x="7"/>
-        <item t="data" sd="1" m="1" x="21"/>
-        <item t="data" sd="1" x="1"/>
-        <item t="data" sd="1" x="2"/>
-        <item t="default" sd="1"/>
+        <item m="1" x="12"/>
+        <item m="1" x="16"/>
+        <item m="1" x="29"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="0"/>
+        <item m="1" x="17"/>
+        <item m="1" x="33"/>
+        <item m="1" x="26"/>
+        <item m="1" x="13"/>
+        <item m="1" x="9"/>
+        <item m="1" x="25"/>
+        <item m="1" x="8"/>
+        <item m="1" x="28"/>
+        <item m="1" x="19"/>
+        <item m="1" x="30"/>
+        <item m="1" x="15"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item m="1" x="10"/>
+        <item m="1" x="18"/>
+        <item m="1" x="11"/>
+        <item m="1" x="22"/>
+        <item m="1" x="32"/>
+        <item m="1" x="20"/>
+        <item m="1" x="27"/>
+        <item m="1" x="14"/>
+        <item m="1" x="23"/>
+        <item m="1" x="7"/>
+        <item m="1" x="21"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
     <field x="2"/>
   </rowFields>
   <rowItems count="8">
-    <i t="data" r="0" i="0">
+    <i>
       <x v="3"/>
       <x v="2"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="3"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="4"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="6"/>
     </i>
-    <i t="default" r="0" i="0">
+    <i t="default">
       <x v="3"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="5"/>
       <x v="4"/>
     </i>
-    <i t="default" r="0" i="0">
+    <i t="default">
       <x v="5"/>
     </i>
-    <i t="grand" r="0" i="0">
-      <x v="0"/>
+    <i t="grand">
+      <x/>
     </i>
   </rowItems>
   <colFields count="1">
     <field x="12"/>
   </colFields>
   <colItems count="8">
-    <i t="data" r="0" i="0">
+    <i>
       <x v="5"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="17"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="18"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="19"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="20"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="32"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="33"/>
     </i>
-    <i t="grand" r="0" i="0">
-      <x v="0"/>
+    <i t="grand">
+      <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Status" fld="12" subtotal="count" showDataAs="normal" baseField="0" baseItem="0"/>
+    <dataField name="Count of Status" fld="12" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="44">
-    <format action="formatting" dxfId="43">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
+    <format dxfId="43">
+      <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="42">
+    <format dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="41">
+    <format dxfId="41">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="40">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="39">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="38">
+    <format dxfId="38">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="37">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="36">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="35">
+    <format dxfId="35">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="34">
+    <format dxfId="34">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="33">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="32">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="31">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="30">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="29">
+    <format dxfId="29">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="28">
+    <format dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="27">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12">
+          <reference field="12" count="5">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4200,10 +4843,10 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="26">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="26">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" selected="0">
+          <reference field="12" count="5" selected="0">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4213,16 +4856,16 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="25">
+    <format dxfId="25">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="24">
+    <format dxfId="24">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="23">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12">
+          <reference field="12" count="5">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4232,176 +4875,181 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="22">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0">
+          <reference field="0" count="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="21">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="20">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="19">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0">
+          <reference field="0" count="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="18">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="17">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="2"/>
           </reference>
-          <reference field="2">
+          <reference field="2" count="1">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="16">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="15">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="15">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0" defaultSubtotal="1">
+          <reference field="0" count="1" selected="0" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="14">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="13">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="13">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0" defaultSubtotal="1">
+          <reference field="0" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="12">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="12">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="5"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="11">
+    <format dxfId="11">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="10">
+    <format dxfId="10">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="9">
+    <format dxfId="9">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="8">
+    <format dxfId="8">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="7">
+    <format dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="6">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0"/>
+          <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="5">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="4">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="3"/>
           </reference>
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="3">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="5"/>
           </reference>
-          <reference field="2">
+          <reference field="2" count="2">
             <x v="4"/>
             <x v="6"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="2">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="1">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12"/>
+          <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="0">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12"/>
+          <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
@@ -4691,1706 +5339,2482 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="25.88671875" customWidth="1" style="38" min="1" max="2"/>
-    <col width="25" customWidth="1" style="38" min="3" max="3"/>
-    <col width="25.88671875" customWidth="1" style="38" min="4" max="4"/>
-    <col width="34.88671875" customWidth="1" style="38" min="5" max="5"/>
-    <col width="40.88671875" customWidth="1" style="38" min="6" max="14"/>
-    <col width="9.109375" customWidth="1" style="38" min="15" max="16384"/>
+    <col min="1" max="2" width="25.88671875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="25" style="38" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" style="38" customWidth="1"/>
+    <col min="6" max="14" width="40.88671875" style="38" customWidth="1"/>
+    <col min="15" max="16384" width="9.109375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scenario Owner: </t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="36" t="n"/>
-      <c r="E1" s="37" t="n"/>
-    </row>
-    <row r="2" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Test Cycle:</t>
-        </is>
-      </c>
-      <c r="B2" s="96" t="n"/>
-      <c r="C2" s="123" t="n"/>
-      <c r="D2" s="97" t="n"/>
-      <c r="E2" s="41" t="n"/>
-    </row>
-    <row r="3" ht="12" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>Scenario ID:</t>
-        </is>
-      </c>
-      <c r="B3" s="124" t="inlineStr">
-        <is>
-          <t>GPO-001</t>
-        </is>
-      </c>
-      <c r="C3" s="125" t="n"/>
-      <c r="D3" s="125" t="n"/>
-      <c r="E3" s="126" t="n"/>
-    </row>
-    <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>Test Objective:</t>
-        </is>
-      </c>
-      <c r="B4" s="124" t="inlineStr">
-        <is>
-          <t>Create PR and PO in guided buying.</t>
-        </is>
-      </c>
-      <c r="C4" s="125" t="n"/>
-      <c r="D4" s="125" t="n"/>
-      <c r="E4" s="126" t="n"/>
-    </row>
-    <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="127" t="inlineStr">
-        <is>
-          <t>Scenario Description:</t>
-        </is>
-      </c>
-      <c r="B5" s="105" t="n"/>
-      <c r="E5" s="128" t="n"/>
-    </row>
-    <row r="6" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A6" s="129" t="n"/>
-      <c r="B6" s="130" t="n"/>
-      <c r="C6" s="130" t="n"/>
-      <c r="D6" s="130" t="n"/>
-      <c r="E6" s="131" t="n"/>
-    </row>
-    <row r="7" ht="12" customHeight="1" thickBot="1">
-      <c r="A7" s="42" t="n"/>
-      <c r="E7" s="43" t="n"/>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="127" t="inlineStr">
-        <is>
-          <t>Long Description Scenario Summary for items to be tested</t>
-        </is>
-      </c>
-      <c r="B8" s="132" t="n"/>
-      <c r="C8" s="132" t="n"/>
-      <c r="D8" s="132" t="n"/>
-      <c r="E8" s="133" t="n"/>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="134" t="inlineStr">
-        <is>
-          <t>Search catalog for items
-Add items to cart
-Complete requisition details and submit
-Review PR approval flow 
-Confirm PO generation
-Create associated receipt</t>
-        </is>
-      </c>
-      <c r="B9" s="135" t="n"/>
-      <c r="C9" s="135" t="n"/>
-      <c r="D9" s="135" t="n"/>
-      <c r="E9" s="136" t="n"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="137" t="n"/>
-      <c r="E10" s="128" t="n"/>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="137" t="n"/>
-      <c r="E11" s="128" t="n"/>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="137" t="n"/>
-      <c r="E12" s="128" t="n"/>
-      <c r="F12" s="38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="137" t="n"/>
-      <c r="E13" s="128" t="n"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="137" t="n"/>
-      <c r="E14" s="128" t="n"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A15" s="137" t="n"/>
-      <c r="E15" s="128" t="n"/>
-    </row>
-    <row r="16" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>Data Requirements</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>Legacy Reference</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>SAP Reference</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="E16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="69" t="n"/>
-      <c r="B17" s="113" t="n"/>
-      <c r="C17" s="95" t="n"/>
-      <c r="D17" s="138" t="n"/>
-      <c r="E17" s="136" t="n"/>
-    </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="A18" s="67" t="n"/>
-      <c r="B18" s="95" t="n"/>
-      <c r="C18" s="95" t="n"/>
-      <c r="D18" s="137" t="n"/>
-      <c r="E18" s="128" t="n"/>
-    </row>
-    <row r="19" ht="12" customHeight="1">
-      <c r="A19" s="68" t="n"/>
-      <c r="B19" s="95" t="n"/>
-      <c r="C19" s="95" t="n"/>
-      <c r="D19" s="137" t="n"/>
-      <c r="E19" s="128" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="95" t="n"/>
-      <c r="C20" s="95" t="n"/>
-      <c r="D20" s="137" t="n"/>
-      <c r="E20" s="128" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="95" t="n"/>
-      <c r="D21" s="137" t="n"/>
-      <c r="E21" s="128" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="112" t="n"/>
-      <c r="B22" s="113" t="n"/>
-      <c r="C22" s="95" t="n"/>
-      <c r="D22" s="137" t="n"/>
-      <c r="E22" s="128" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="112" t="n"/>
-      <c r="B23" s="113" t="n"/>
-      <c r="C23" s="95" t="n"/>
-      <c r="D23" s="137" t="n"/>
-      <c r="E23" s="128" t="n"/>
-    </row>
-    <row r="24" ht="12" customHeight="1" thickBot="1">
-      <c r="A24" s="51" t="n"/>
-      <c r="D24" s="137" t="n"/>
-      <c r="E24" s="128" t="n"/>
-    </row>
-    <row r="25" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prerequisite </t>
-        </is>
-      </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
-      <c r="D25" s="45" t="n"/>
-      <c r="E25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="94" t="n"/>
-      <c r="E26" s="43" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="94" t="n"/>
-      <c r="E27" s="43" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="94" t="n"/>
-      <c r="E28" s="43" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="94" t="n"/>
-      <c r="E29" s="43" t="n"/>
-    </row>
-    <row r="30" ht="12" customHeight="1" thickBot="1">
-      <c r="A30" s="51" t="n"/>
-      <c r="E30" s="43" t="n"/>
-    </row>
-    <row r="31" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A31" s="44" t="inlineStr">
-        <is>
-          <t>Key RICEF Objects</t>
-        </is>
-      </c>
-      <c r="B31" s="45" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="46" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="94" t="inlineStr">
-        <is>
-          <t>Master Data Validation</t>
-        </is>
-      </c>
-      <c r="E32" s="43" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="94" t="inlineStr">
-        <is>
-          <t>SAP PO Post and Validation</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="94" t="inlineStr">
-        <is>
-          <t>SAP Invoice to SAP</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="n"/>
-    </row>
-    <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="94" t="inlineStr">
-        <is>
-          <t>Payment Remitance Validation to Ariba</t>
-        </is>
-      </c>
-      <c r="E35" s="52" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="117" t="n"/>
-      <c r="C36" s="119" t="n"/>
-      <c r="E36" s="43" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="117" t="n"/>
-      <c r="C37" s="119" t="n"/>
-      <c r="E37" s="43" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1" thickBot="1">
-      <c r="A38" s="53" t="inlineStr">
-        <is>
-          <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="n"/>
-    </row>
-    <row r="39" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A39" s="54" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B39" s="55" t="inlineStr">
-        <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="C39" s="55" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D39" s="55" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="E39" s="46" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="109" t="n"/>
-      <c r="B40" s="110" t="n"/>
-      <c r="C40" s="110" t="n"/>
-      <c r="D40" s="110" t="n"/>
-      <c r="E40" s="58" t="n"/>
-    </row>
-    <row r="41" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A41" s="59" t="n"/>
-      <c r="B41" s="60" t="n"/>
-      <c r="C41" s="60" t="n"/>
-      <c r="D41" s="60" t="n"/>
-      <c r="E41" s="61" t="n"/>
-    </row>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12" customHeight="1"/>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="62" t="n"/>
-      <c r="B47" s="63" t="n"/>
-      <c r="C47" s="63" t="n"/>
-      <c r="D47" s="63" t="n"/>
-    </row>
-    <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="62" t="n"/>
-      <c r="B48" s="63" t="n"/>
-      <c r="C48" s="63" t="n"/>
-      <c r="D48" s="63" t="n"/>
-    </row>
-    <row r="49" ht="13.2" customHeight="1">
-      <c r="A49" s="64" t="n"/>
-      <c r="B49" s="65" t="n"/>
-      <c r="C49" s="66" t="n"/>
-      <c r="D49" s="65" t="n"/>
-      <c r="E49" s="65" t="n"/>
-    </row>
-    <row r="50" ht="13.2" customHeight="1">
-      <c r="A50" s="63" t="n"/>
-      <c r="B50" s="63" t="n"/>
-      <c r="C50" s="63" t="n"/>
-      <c r="D50" s="63" t="n"/>
-    </row>
-    <row r="51" ht="13.2" customHeight="1">
-      <c r="A51" s="63" t="n"/>
-      <c r="B51" s="63" t="n"/>
-      <c r="C51" s="63" t="n"/>
-      <c r="D51" s="63" t="n"/>
-    </row>
-    <row r="52" ht="13.2" customHeight="1">
-      <c r="A52" s="63" t="n"/>
-      <c r="B52" s="63" t="n"/>
-      <c r="C52" s="63" t="n"/>
-      <c r="D52" s="63" t="n"/>
-    </row>
-    <row r="53" ht="13.2" customHeight="1">
-      <c r="A53" s="63" t="n"/>
-      <c r="B53" s="63" t="n"/>
-      <c r="C53" s="63" t="n"/>
-      <c r="D53" s="63" t="n"/>
-    </row>
-    <row r="54" ht="13.2" customHeight="1">
-      <c r="A54" s="63" t="n"/>
-      <c r="B54" s="63" t="n"/>
-      <c r="C54" s="63" t="n"/>
-      <c r="D54" s="63" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="62" t="n"/>
-      <c r="B55" s="63" t="n"/>
-      <c r="C55" s="63" t="n"/>
-      <c r="D55" s="63" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="62" t="n"/>
-      <c r="B56" s="63" t="n"/>
-      <c r="C56" s="63" t="n"/>
-      <c r="D56" s="63" t="n"/>
-    </row>
-    <row r="57" ht="13.2" customHeight="1">
-      <c r="A57" s="63" t="n"/>
-      <c r="B57" s="63" t="n"/>
-      <c r="C57" s="63" t="n"/>
-      <c r="D57" s="63" t="n"/>
-      <c r="E57" s="63" t="n"/>
-    </row>
-    <row r="58" ht="13.2" customHeight="1">
-      <c r="A58" s="63" t="n"/>
-      <c r="B58" s="63" t="n"/>
-      <c r="C58" s="63" t="n"/>
-      <c r="D58" s="63" t="n"/>
-      <c r="E58" s="63" t="n"/>
-    </row>
-    <row r="59" ht="13.2" customHeight="1">
-      <c r="A59" s="63" t="n"/>
-      <c r="B59" s="63" t="n"/>
-      <c r="C59" s="63" t="n"/>
-      <c r="D59" s="63" t="n"/>
-      <c r="E59" s="63" t="n"/>
-    </row>
-    <row r="60" ht="13.2" customHeight="1">
-      <c r="A60" s="63" t="n"/>
-      <c r="B60" s="63" t="n"/>
-      <c r="C60" s="63" t="n"/>
-      <c r="D60" s="63" t="n"/>
-      <c r="E60" s="63" t="n"/>
-    </row>
-    <row r="61" ht="13.2" customHeight="1">
-      <c r="A61" s="63" t="n"/>
-      <c r="B61" s="63" t="n"/>
-      <c r="C61" s="63" t="n"/>
-      <c r="D61" s="63" t="n"/>
-      <c r="E61" s="63" t="n"/>
-    </row>
-    <row r="62" ht="13.2" customHeight="1">
-      <c r="A62" s="63" t="n"/>
-      <c r="B62" s="63" t="n"/>
-      <c r="C62" s="63" t="n"/>
-      <c r="D62" s="63" t="n"/>
-      <c r="E62" s="63" t="n"/>
-    </row>
-    <row r="63" ht="13.2" customHeight="1">
-      <c r="A63" s="63" t="n"/>
-      <c r="B63" s="63" t="n"/>
-      <c r="C63" s="63" t="n"/>
-      <c r="D63" s="63" t="n"/>
-      <c r="E63" s="63" t="n"/>
-    </row>
-    <row r="64" ht="13.2" customHeight="1">
-      <c r="A64" s="63" t="n"/>
-      <c r="B64" s="63" t="n"/>
-      <c r="C64" s="63" t="n"/>
-      <c r="D64" s="63" t="n"/>
-      <c r="E64" s="63" t="n"/>
-    </row>
-    <row r="65" ht="13.2" customHeight="1">
-      <c r="A65" s="63" t="n"/>
-      <c r="B65" s="63" t="n"/>
-      <c r="C65" s="63" t="n"/>
-      <c r="D65" s="63" t="n"/>
-      <c r="E65" s="63" t="n"/>
-    </row>
-    <row r="66" ht="13.2" customHeight="1">
-      <c r="A66" s="63" t="n"/>
-      <c r="B66" s="63" t="n"/>
-      <c r="C66" s="63" t="n"/>
-      <c r="D66" s="63" t="n"/>
-      <c r="E66" s="63" t="n"/>
-    </row>
-    <row r="67" ht="13.2" customHeight="1">
-      <c r="A67" s="63" t="n"/>
-      <c r="B67" s="63" t="n"/>
-      <c r="C67" s="63" t="n"/>
-      <c r="D67" s="63" t="n"/>
-      <c r="E67" s="63" t="n"/>
-    </row>
-    <row r="68" ht="13.2" customHeight="1">
-      <c r="A68" s="63" t="n"/>
-      <c r="B68" s="63" t="n"/>
-      <c r="C68" s="63" t="n"/>
-      <c r="D68" s="63" t="n"/>
-      <c r="E68" s="63" t="n"/>
-    </row>
-    <row r="69" ht="13.2" customHeight="1">
-      <c r="A69" s="63" t="n"/>
-      <c r="B69" s="63" t="n"/>
-      <c r="C69" s="63" t="n"/>
-      <c r="D69" s="63" t="n"/>
-      <c r="E69" s="63" t="n"/>
-    </row>
-    <row r="70" ht="13.2" customHeight="1">
-      <c r="A70" s="63" t="n"/>
-      <c r="B70" s="63" t="n"/>
-      <c r="C70" s="63" t="n"/>
-      <c r="D70" s="63" t="n"/>
-      <c r="E70" s="63" t="n"/>
+    <row r="1" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41"/>
+    </row>
+    <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="98" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="100"/>
+    </row>
+    <row r="4" spans="1:6" ht="12" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="100"/>
+    </row>
+    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="103"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="102"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="105"/>
+    </row>
+    <row r="7" spans="1:6" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="E7" s="43"/>
+    </row>
+    <row r="8" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="108"/>
+    </row>
+    <row r="9" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="112"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="112"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114"/>
+    </row>
+    <row r="12" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="112"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="112"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="114"/>
+    </row>
+    <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="112"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="114"/>
+    </row>
+    <row r="15" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="112"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="114"/>
+    </row>
+    <row r="16" spans="1:6" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="46"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="69"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="116"/>
+    </row>
+    <row r="18" spans="1:5" ht="12" x14ac:dyDescent="0.25">
+      <c r="A18" s="67"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="118"/>
+    </row>
+    <row r="19" spans="1:5" ht="12" x14ac:dyDescent="0.25">
+      <c r="A19" s="68"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="118"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="118"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="50"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="118"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="118"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="118"/>
+    </row>
+    <row r="24" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="51"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="118"/>
+    </row>
+    <row r="25" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="46"/>
+    </row>
+    <row r="26" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="94"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="94"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="43"/>
+    </row>
+    <row r="30" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
+      <c r="E30" s="43"/>
+    </row>
+    <row r="31" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="46"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="43"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="95"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="43"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="95"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="43"/>
+    </row>
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="95"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="52"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="117"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="43"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="117"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="43"/>
+    </row>
+    <row r="38" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="43"/>
+    </row>
+    <row r="39" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="46"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="56"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
+    </row>
+    <row r="41" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="59"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
+    </row>
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="62"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+    </row>
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="62"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+    </row>
+    <row r="49" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A49" s="64"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="65"/>
+    </row>
+    <row r="50" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A50" s="63"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+    </row>
+    <row r="51" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A51" s="63"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+    </row>
+    <row r="52" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A52" s="63"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+    </row>
+    <row r="53" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A53" s="63"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+    </row>
+    <row r="54" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A54" s="63"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+    </row>
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="62"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+    </row>
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="62"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+    </row>
+    <row r="57" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" s="63"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+    </row>
+    <row r="58" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A58" s="63"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+    </row>
+    <row r="59" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A59" s="63"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+    </row>
+    <row r="60" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A60" s="63"/>
+      <c r="B60" s="63"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+    </row>
+    <row r="61" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A61" s="63"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+    </row>
+    <row r="62" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A62" s="63"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+    </row>
+    <row r="63" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A63" s="63"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+    </row>
+    <row r="64" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A64" s="63"/>
+      <c r="B64" s="63"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+    </row>
+    <row r="65" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A65" s="63"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+    </row>
+    <row r="66" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A66" s="63"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+    </row>
+    <row r="67" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A67" s="63"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+    </row>
+    <row r="68" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A68" s="63"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+    </row>
+    <row r="69" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A69" s="63"/>
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+    </row>
+    <row r="70" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A70" s="63"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="63"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:E6"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A9:E15"/>
     <mergeCell ref="D17:E24"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B5:E6"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D2:E2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E2">
       <formula1>"R4-Cycle 1,R4-Cycle 2,R4-Cycle 3,R4-Cycle 4,R4-Regression Test,R4-Business Simulation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" scale="69"/>
+  <pageSetup scale="69" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="35.6640625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="35.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10.33203125" customWidth="1" style="86" min="1" max="1"/>
-    <col width="18.6640625" customWidth="1" style="86" min="2" max="2"/>
-    <col width="10.33203125" customWidth="1" style="72" min="3" max="3"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" style="72" min="4" max="4"/>
-    <col width="14" customWidth="1" style="86" min="5" max="5"/>
-    <col width="80.44140625" customWidth="1" style="87" min="6" max="6"/>
-    <col width="62.44140625" customWidth="1" style="72" min="7" max="7"/>
-    <col width="46.44140625" customWidth="1" style="72" min="8" max="8"/>
-    <col width="15.88671875" customWidth="1" style="72" min="9" max="9"/>
-    <col width="41.33203125" customWidth="1" style="72" min="10" max="10"/>
-    <col width="18.88671875" customWidth="1" style="86" min="11" max="11"/>
-    <col width="18.6640625" customWidth="1" style="72" min="12" max="12"/>
-    <col width="17.44140625" customWidth="1" style="72" min="13" max="13"/>
-    <col width="16.44140625" customWidth="1" style="87" min="14" max="14"/>
-    <col width="13.33203125" customWidth="1" style="87" min="15" max="15"/>
-    <col width="37.109375" bestFit="1" customWidth="1" style="72" min="16" max="16"/>
-    <col width="9.109375" customWidth="1" style="72" min="17" max="17"/>
-    <col width="35.6640625" customWidth="1" style="72" min="18" max="16384"/>
+    <col min="1" max="1" width="10.33203125" style="86" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="86" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="72" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="72" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="86" customWidth="1"/>
+    <col min="6" max="6" width="80.44140625" style="87" customWidth="1"/>
+    <col min="7" max="7" width="62.44140625" style="72" customWidth="1"/>
+    <col min="8" max="8" width="46.44140625" style="72" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" style="72" customWidth="1"/>
+    <col min="10" max="10" width="41.33203125" style="72" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" style="86" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" style="72" customWidth="1"/>
+    <col min="13" max="13" width="17.44140625" style="72" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="87" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" style="87" customWidth="1"/>
+    <col min="16" max="16" width="37.109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" style="72"/>
+    <col min="18" max="16384" width="35.6640625" style="72"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="120" t="inlineStr">
-        <is>
-          <t>Scenario Number</t>
-        </is>
-      </c>
-      <c r="B1" s="120" t="n"/>
-      <c r="C1" s="120" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D1" s="120" t="n"/>
-      <c r="E1" s="120" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="F1" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Description </t>
-        </is>
-      </c>
-      <c r="G1" s="120" t="inlineStr">
-        <is>
-          <t>Test Data / Test Execution</t>
-        </is>
-      </c>
-      <c r="H1" s="120" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="I1" s="121" t="inlineStr">
-        <is>
-          <t>Step Completed
-Sucessfullyåç</t>
-        </is>
-      </c>
-      <c r="J1" s="120" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="K1" s="120" t="inlineStr">
-        <is>
-          <t>FI Impact</t>
-        </is>
-      </c>
-      <c r="L1" s="120" t="inlineStr">
-        <is>
-          <t>RICEF Tested</t>
-        </is>
-      </c>
-      <c r="M1" s="120" t="inlineStr">
-        <is>
-          <t>TPR #</t>
-        </is>
-      </c>
-      <c r="N1" s="120" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="O1" s="122" t="inlineStr">
-        <is>
-          <t>Tester/User ID</t>
-        </is>
-      </c>
-      <c r="P1" s="120" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="139" t="n"/>
-      <c r="B2" s="120" t="n"/>
-      <c r="C2" s="139" t="n"/>
-      <c r="D2" s="73" t="n"/>
-      <c r="E2" s="139" t="n"/>
-      <c r="F2" s="139" t="n"/>
-      <c r="G2" s="139" t="n"/>
-      <c r="H2" s="139" t="n"/>
-      <c r="I2" s="140" t="n"/>
-      <c r="J2" s="139" t="n"/>
-      <c r="K2" s="73" t="inlineStr">
-        <is>
-          <t>Y or N</t>
-        </is>
-      </c>
-      <c r="L2" s="139" t="n"/>
-      <c r="M2" s="139" t="n"/>
-      <c r="N2" s="139" t="n"/>
-      <c r="O2" s="141" t="n"/>
-      <c r="P2" s="139" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="74" t="n"/>
-      <c r="B3" s="74" t="inlineStr">
-        <is>
-          <t>Scenario No.</t>
-        </is>
-      </c>
-      <c r="C3" s="74" t="n"/>
-      <c r="D3" s="74" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="E3" s="74" t="n"/>
-      <c r="F3" s="75" t="n"/>
-      <c r="G3" s="76" t="n"/>
-      <c r="H3" s="76" t="n"/>
-      <c r="I3" s="76" t="n"/>
-      <c r="J3" s="74" t="n"/>
-      <c r="K3" s="74" t="n"/>
-      <c r="L3" s="74" t="n"/>
-      <c r="M3" s="74" t="n"/>
-      <c r="N3" s="77" t="n"/>
-      <c r="O3" s="77" t="n"/>
-      <c r="P3" s="74" t="n"/>
-    </row>
-    <row r="4" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A4" s="70" t="inlineStr">
-        <is>
-          <t>BL_001</t>
-        </is>
-      </c>
-      <c r="B4" s="70" t="inlineStr">
-        <is>
-          <t>GPO-001</t>
-        </is>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="120" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="71"/>
+      <c r="E1" s="120" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="120"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="120"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="74"/>
+    </row>
+    <row r="4" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A4" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="70">
-        <f>ROW(A4)-3</f>
-        <v/>
-      </c>
-      <c r="D4" s="70" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="E4" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F4" s="70" t="inlineStr">
-        <is>
-          <t>Complete script GEN-002 to log into Ariba "Advanced" Buying and Invoicing.</t>
-        </is>
-      </c>
-      <c r="G4" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Login
-Password
-</t>
-        </is>
-      </c>
-      <c r="H4" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nexus Water Group homepage is presented. </t>
-        </is>
+        <f t="shared" ref="C4:C9" si="0">ROW(A4)-3</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="79" t="s">
+        <v>83</v>
       </c>
       <c r="I4" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J4" s="70" t="n"/>
-      <c r="K4" s="70" t="n"/>
-      <c r="L4" s="70" t="n"/>
-      <c r="M4" s="70" t="n"/>
-      <c r="N4" s="70" t="n"/>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="70" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="81">
-      <c r="A5" s="70" t="n"/>
-      <c r="B5" s="70" t="n"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+    </row>
+    <row r="5" spans="1:16" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="70"/>
+      <c r="B5" s="70"/>
       <c r="C5" s="70">
-        <f>ROW(A5)-3</f>
-        <v/>
-      </c>
-      <c r="D5" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E5" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F5" s="89" t="inlineStr">
-        <is>
-          <t>Click on Catalog Tab</t>
-        </is>
-      </c>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="70" t="inlineStr">
-        <is>
-          <t>Catalog page is displayed</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="78"/>
+      <c r="H5" s="70" t="s">
+        <v>85</v>
       </c>
       <c r="I5" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="70" t="n"/>
-      <c r="K5" s="70" t="n"/>
-      <c r="L5" s="70" t="n"/>
-      <c r="M5" s="70" t="n"/>
-      <c r="N5" s="70" t="n"/>
-      <c r="O5" s="70" t="n"/>
-      <c r="P5" s="70" t="n"/>
-    </row>
-    <row r="6" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A6" s="70" t="n"/>
-      <c r="B6" s="70" t="n"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+    </row>
+    <row r="6" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A6" s="70"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="70">
-        <f>ROW(A6)-3</f>
-        <v/>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>On the search bar where it says "Search by part #, supplier name or keyword", type in the item you want to purchase.</t>
-        </is>
-      </c>
-      <c r="G6" s="78" t="inlineStr">
-        <is>
-          <t>AT-12</t>
-        </is>
-      </c>
-      <c r="H6" s="70" t="n"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="70"/>
       <c r="I6" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="70" t="n"/>
-      <c r="K6" s="70" t="n"/>
-      <c r="L6" s="70" t="n"/>
-      <c r="M6" s="70" t="n"/>
-      <c r="N6" s="70" t="n"/>
-      <c r="O6" s="70" t="n"/>
-      <c r="P6" s="70" t="n"/>
-    </row>
-    <row r="7" ht="39.75" customFormat="1" customHeight="1" s="81">
-      <c r="A7" s="70" t="n"/>
-      <c r="B7" s="70" t="n"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+    </row>
+    <row r="7" spans="1:16" s="81" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="70"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="70">
-        <f>ROW(A7)-3</f>
-        <v/>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E7" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F7" s="70" t="inlineStr">
-        <is>
-          <t>From the search result, find the item. Enter the desired quantity  in the "Qty" box.</t>
-        </is>
-      </c>
-      <c r="G7" s="78" t="inlineStr">
-        <is>
-          <t>Quantity : 4</t>
-        </is>
-      </c>
-      <c r="H7" s="70" t="inlineStr">
-        <is>
-          <t>Desired quantity is indicated.</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="78" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>45</v>
       </c>
       <c r="I7" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="70" t="n"/>
-      <c r="K7" s="70" t="n"/>
-      <c r="L7" s="70" t="n"/>
-      <c r="M7" s="70" t="n"/>
-      <c r="N7" s="70" t="n"/>
-      <c r="O7" s="70" t="n"/>
-      <c r="P7" s="70" t="n"/>
-    </row>
-    <row r="8" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A8" s="70" t="n"/>
-      <c r="B8" s="70" t="n"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+    </row>
+    <row r="8" spans="1:16" s="81" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="70"/>
+      <c r="B8" s="70"/>
       <c r="C8" s="70">
-        <f>ROW(A8)-3</f>
-        <v/>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E8" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F8" s="70" t="inlineStr">
-        <is>
-          <t>Press "Add to Cart" button.</t>
-        </is>
-      </c>
-      <c r="G8" s="70" t="inlineStr">
-        <is>
-          <t>No.: 1
-Full Description: Book Bins - Set of 16
-Supplier Part Number: AA750X
-Supplier Part Auxiliary ID: 
-Qty: 5
-UOM: each
-Price: $94.50 USD
-Price Unit Quantity: 1
-Unit Conversion: 
-Pricing Description: 
-Discount: 
-Net Amount: $472.50 USD Fx
-Charges: 
-Taxes: 
-Amount: $472.50 USD
-Commodity Code: Containers and storage
-Supplier: LAKESHORE LEARNING MATERIALS
-Contact: LAKESHORE LEARNING MATERIALS [ select ]
-Service Item: No
-Contract: [ select ]</t>
-        </is>
-      </c>
-      <c r="H8" s="70" t="inlineStr">
-        <is>
-          <t>Shopping Cart popup  window appears.</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70" t="s">
+        <v>47</v>
       </c>
       <c r="I8" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="70" t="n"/>
-      <c r="K8" s="70" t="n"/>
-      <c r="L8" s="70" t="n"/>
-      <c r="M8" s="70" t="n"/>
-      <c r="N8" s="70" t="n"/>
-      <c r="O8" s="70" t="n"/>
-      <c r="P8" s="70" t="n"/>
-    </row>
-    <row r="9" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A9" s="70" t="n"/>
-      <c r="B9" s="70" t="n"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+    </row>
+    <row r="9" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="70">
-        <f>ROW(A9)-3</f>
-        <v/>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E9" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F9" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen. Click on Proceed to Checkout button.
-</t>
-        </is>
-      </c>
-      <c r="G9" s="88" t="inlineStr">
-        <is>
-          <t>
-</t>
-        </is>
-      </c>
-      <c r="H9" s="82" t="inlineStr">
-        <is>
-          <t>Requisition screen appears. The system assigns the PR number to the document.</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="82" t="s">
+        <v>49</v>
       </c>
       <c r="I9" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="70" t="n"/>
-      <c r="K9" s="70" t="n"/>
-      <c r="L9" s="70" t="n"/>
-      <c r="M9" s="70" t="n"/>
-      <c r="N9" s="70" t="n"/>
-      <c r="O9" s="70" t="n"/>
-      <c r="P9" s="70" t="n"/>
-    </row>
-    <row r="10" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A10" s="70" t="n"/>
-      <c r="B10" s="70" t="n"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+    </row>
+    <row r="10" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
       <c r="C10" s="70">
-        <f>ROW(A10)-3</f>
-        <v/>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header</t>
-        </is>
-      </c>
-      <c r="E10" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F10" s="83" t="inlineStr">
-        <is>
-          <t>Enter the requistion title on "Requistion title" box.</t>
-        </is>
-      </c>
-      <c r="G10" s="78" t="inlineStr">
-        <is>
-          <t>AT-1</t>
-        </is>
-      </c>
-      <c r="H10" s="70" t="inlineStr">
-        <is>
-          <t>Requisition title is updated.</t>
-        </is>
+        <f t="shared" ref="C10:C17" si="1">ROW(A10)-3</f>
+        <v>7</v>
+      </c>
+      <c r="D10" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="70" t="s">
+        <v>52</v>
       </c>
       <c r="I10" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="70" t="n"/>
-      <c r="K10" s="70" t="n"/>
-      <c r="L10" s="70" t="n"/>
-      <c r="M10" s="70" t="n"/>
-      <c r="N10" s="70" t="n"/>
-      <c r="O10" s="70" t="n"/>
-      <c r="P10" s="70" t="n"/>
-    </row>
-    <row r="11" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A11" s="70" t="n"/>
-      <c r="B11" s="70" t="n"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+    </row>
+    <row r="11" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
       <c r="C11" s="70">
-        <f>ROW(A11)-3</f>
-        <v/>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header</t>
-        </is>
-      </c>
-      <c r="E11" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F11" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enter or verify the remaing data elements on the Requistion screen.
-Note: Only "red " items should be editable.
-</t>
-        </is>
-      </c>
-      <c r="G11" s="90" t="inlineStr">
-        <is>
-          <t>Account Type: Expense
-Bill To: Ariba - Pittsburgh
-Cost Center: Ariba - Office of the CEO
-Business Unit: Ariba - Marketing
-Company: Ariba - Company 1
-Account: ARIBA - Expense Account 1
-Project: (no value)</t>
-        </is>
-      </c>
-      <c r="H11" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated without any error.</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="90"/>
+      <c r="H11" s="70" t="s">
+        <v>54</v>
       </c>
       <c r="I11" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>Need-by is Today +5</t>
-        </is>
-      </c>
-      <c r="K11" s="70" t="n"/>
-      <c r="L11" s="70" t="n"/>
-      <c r="M11" s="70" t="n"/>
-      <c r="N11" s="70" t="n"/>
-      <c r="O11" s="70" t="n"/>
-      <c r="P11" s="70" t="n"/>
-    </row>
-    <row r="12" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A12" s="70" t="n"/>
-      <c r="B12" s="70" t="n"/>
+      <c r="J11" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+    </row>
+    <row r="12" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
       <c r="C12" s="70">
-        <f>ROW(A12)-3</f>
-        <v/>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E12" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F12" s="91" t="inlineStr">
-        <is>
-          <t>Click on the checkbox in the line for the item (towards the item lines' top left).
-Click on Actions dropdown and then Edit Details.</t>
-        </is>
-      </c>
-      <c r="G12" s="92" t="inlineStr">
-        <is>
-          <t>Ship_To: Ariba - Pittsburgh
-Deliver_To: Samit Paudel
-Need-by_Date: Tue, 22 Apr, 2025</t>
-        </is>
-      </c>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>Edit Detail page for the item is displayed.</t>
-        </is>
-      </c>
-      <c r="I12" s="80" t="n"/>
-      <c r="J12" s="70" t="n"/>
-      <c r="K12" s="70" t="n"/>
-      <c r="L12" s="70" t="n"/>
-      <c r="M12" s="70" t="n"/>
-      <c r="N12" s="70" t="n"/>
-      <c r="O12" s="70" t="n"/>
-      <c r="P12" s="70" t="n"/>
-    </row>
-    <row r="13" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A13" s="70" t="n"/>
-      <c r="B13" s="70" t="n"/>
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="91" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="92"/>
+      <c r="H12" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="80"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+    </row>
+    <row r="13" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
       <c r="C13" s="70">
-        <f>ROW(A13)-3</f>
-        <v/>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E13" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F13" s="91" t="inlineStr">
-        <is>
-          <t>Enter or verify the Line Item Details for the item.
-(Most details in this section is set to default)</t>
-        </is>
-      </c>
-      <c r="G13" s="92" t="n"/>
-      <c r="H13" s="90" t="inlineStr">
-        <is>
-          <t>Fields are validated and updated if necessary.</t>
-        </is>
-      </c>
-      <c r="I13" s="80" t="n"/>
-      <c r="J13" s="70" t="n"/>
-      <c r="K13" s="70" t="n"/>
-      <c r="L13" s="70" t="n"/>
-      <c r="M13" s="70" t="n"/>
-      <c r="N13" s="70" t="n"/>
-      <c r="O13" s="70" t="n"/>
-      <c r="P13" s="70" t="n"/>
-    </row>
-    <row r="14" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A14" s="70" t="n"/>
-      <c r="B14" s="70" t="n"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="92"/>
+      <c r="H13" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="80"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+    </row>
+    <row r="14" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
       <c r="C14" s="70">
-        <f>ROW(A14)-3</f>
-        <v/>
-      </c>
-      <c r="D14" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E14" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F14" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scroll down to Accounting - by Line Item Section
-Enter or  verify the information in the Accounting  section. </t>
-        </is>
-      </c>
-      <c r="G14" s="91" t="n"/>
-      <c r="H14" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D14" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="93" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="91"/>
+      <c r="H14" s="70" t="s">
+        <v>57</v>
       </c>
       <c r="I14" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="70" t="n"/>
-      <c r="K14" s="70" t="n"/>
-      <c r="L14" s="70" t="n"/>
-      <c r="M14" s="70" t="n"/>
-      <c r="N14" s="70" t="n"/>
-      <c r="O14" s="70" t="n"/>
-      <c r="P14" s="70" t="n"/>
-    </row>
-    <row r="15" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A15" s="70" t="n"/>
-      <c r="B15" s="70" t="n"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+    </row>
+    <row r="15" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A15" s="70"/>
+      <c r="B15" s="70"/>
       <c r="C15" s="70">
-        <f>ROW(A15)-3</f>
-        <v/>
-      </c>
-      <c r="D15" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E15" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F15" s="90" t="inlineStr">
-        <is>
-          <t>Enter or  verify the information in the Shipping - by Line Item section.</t>
-        </is>
-      </c>
-      <c r="G15" s="90" t="n"/>
-      <c r="H15" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="90"/>
+      <c r="H15" s="70" t="s">
+        <v>57</v>
       </c>
       <c r="I15" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="70" t="n"/>
-      <c r="K15" s="70" t="n"/>
-      <c r="L15" s="70" t="n"/>
-      <c r="M15" s="70" t="n"/>
-      <c r="N15" s="70" t="n"/>
-      <c r="O15" s="70" t="n"/>
-      <c r="P15" s="70" t="n"/>
-    </row>
-    <row r="16" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A16" s="70" t="n"/>
-      <c r="B16" s="70" t="n"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+    </row>
+    <row r="16" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.35">
+      <c r="A16" s="70"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="70">
-        <f>ROW(A16)-3</f>
-        <v/>
-      </c>
-      <c r="D16" s="70" t="inlineStr">
-        <is>
-          <t>Requisition</t>
-        </is>
-      </c>
-      <c r="E16" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F16" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Press "Submit"  to submit the requisition for approval. </t>
-        </is>
-      </c>
-      <c r="G16" s="85" t="n"/>
-      <c r="H16" s="85" t="inlineStr">
-        <is>
-          <t>Message appears "Your requisition has been sent for approval.</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="D16" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85" t="s">
+        <v>60</v>
       </c>
       <c r="I16" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="70" t="n"/>
-      <c r="K16" s="70" t="n"/>
-      <c r="L16" s="70" t="n"/>
-      <c r="M16" s="70" t="n"/>
-      <c r="N16" s="70" t="n"/>
-      <c r="O16" s="70" t="n"/>
-      <c r="P16" s="70" t="n"/>
-    </row>
-    <row r="17" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A17" s="70" t="n"/>
-      <c r="B17" s="70" t="n"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+    </row>
+    <row r="17" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.4">
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="70">
-        <f>ROW(A17)-3</f>
-        <v/>
-      </c>
-      <c r="D17" s="70" t="inlineStr">
-        <is>
-          <t>View Approval Flow</t>
-        </is>
-      </c>
-      <c r="E17" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F17" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Click on View Requisition to display the created requisiton. </t>
-        </is>
-      </c>
-      <c r="G17" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Submitted</t>
-        </is>
-      </c>
-      <c r="H17" s="82" t="inlineStr">
-        <is>
-          <t>The PR is now on Submitted status.
-Approval Flow is now active shown by green flow.</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="82" t="s">
+        <v>64</v>
       </c>
       <c r="I17" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="70" t="n"/>
-      <c r="K17" s="70" t="n"/>
-      <c r="L17" s="70" t="n"/>
-      <c r="M17" s="70" t="n"/>
-      <c r="N17" s="70" t="n"/>
-      <c r="O17" s="70" t="n"/>
-      <c r="P17" s="70" t="n"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="P1:P2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4:N17">
       <formula1>"10 - Not Started,20 - In-Process,30 - TPR Hold,40 - DEV Hold,50 - Pass,60 - N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="K4:K17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K17">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E17">
       <formula1>"AP,Buyer,PO Approv,Inv Approv,Watcher,SAP Tech Team,Prem Tech,Prem Funct"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" scale="61" fitToHeight="10" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="61" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A3:R46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:R46"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="14.88671875" customWidth="1" style="2" min="1" max="1"/>
-    <col width="8.44140625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="14.33203125" customWidth="1" style="2" min="3" max="7"/>
-    <col width="14.33203125" customWidth="1" style="1" min="8" max="9"/>
-    <col width="11.6640625" customWidth="1" style="1" min="10" max="11"/>
-    <col width="14.33203125" bestFit="1" customWidth="1" style="1" min="12" max="17"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="1" min="18" max="18"/>
-    <col width="9.109375" customWidth="1" style="1" min="19" max="16384"/>
+    <col min="1" max="1" width="14.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="2" customWidth="1"/>
+    <col min="3" max="7" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="11.6640625" style="1" customWidth="1"/>
+    <col min="12" max="17" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="17.25" customHeight="1" thickBot="1"/>
-    <row r="3" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Count of Status</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="21" t="n"/>
-    </row>
-    <row r="4" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Scenario Number</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>10 - Not Started</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>20 - In-Process</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>30 - TPR Hold</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
-        <is>
-          <t>40 - DEV Hold</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>50 - Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>60 - N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="13.2" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>PP_018</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>RTR</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="4" t="n">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+    </row>
+    <row r="4" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+    </row>
+    <row r="5" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="6" t="n">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" ht="13.2" customHeight="1">
-      <c r="A6" s="26" t="n"/>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>PTP</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="27" t="n">
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+    </row>
+    <row r="6" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>8</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="27">
         <v>2</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="28">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" ht="13.2" customHeight="1">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n">
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+    </row>
+    <row r="7" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27">
         <v>25</v>
       </c>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="28" t="n">
+      <c r="I7" s="27"/>
+      <c r="J7" s="28">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>IMWM</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n">
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+    </row>
+    <row r="8" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
         <v>5</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="28">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>PP_018 Total</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n">
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+    </row>
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10">
         <v>2</v>
       </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n">
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10">
         <v>38</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="10">
         <v>6</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="11">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>ZZZ999</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="10" t="n">
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+    </row>
+    <row r="10" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10">
         <v>1</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="10">
         <v>1</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="10">
         <v>1</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="10">
         <v>1</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="11">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>ZZZ999 Total</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="4" t="n">
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4">
         <v>1</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="4">
         <v>1</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="10" t="n">
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+    </row>
+    <row r="12" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10">
         <v>3</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="10">
         <v>1</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="10">
         <v>1</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="10">
         <v>1</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="10">
         <v>39</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="10">
         <v>7</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="11">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1"/>
-    <row r="14" ht="17.25" customHeight="1"/>
-    <row r="15" ht="17.25" customHeight="1"/>
-    <row r="16" ht="17.25" customHeight="1"/>
-    <row r="17" ht="17.25" customHeight="1"/>
-    <row r="18" ht="17.25" customHeight="1"/>
-    <row r="19" ht="17.25" customHeight="1"/>
-    <row r="20" ht="17.25" customHeight="1"/>
-    <row r="21" ht="17.25" customHeight="1"/>
-    <row r="22" ht="17.25" customHeight="1"/>
-    <row r="23" ht="17.25" customHeight="1"/>
-    <row r="24" ht="17.25" customHeight="1"/>
-    <row r="25" ht="17.25" customHeight="1"/>
-    <row r="26" ht="17.25" customHeight="1"/>
-    <row r="27" ht="17.25" customHeight="1"/>
-    <row r="28" ht="17.25" customHeight="1"/>
-    <row r="29" ht="17.25" customHeight="1"/>
-    <row r="30" ht="17.25" customHeight="1"/>
-    <row r="31" ht="17.25" customHeight="1"/>
-    <row r="32" ht="17.25" customHeight="1"/>
-    <row r="33" ht="17.25" customHeight="1"/>
-    <row r="34" ht="17.25" customHeight="1"/>
-    <row r="35" ht="17.25" customHeight="1"/>
-    <row r="36" ht="17.25" customHeight="1"/>
-    <row r="37" ht="17.25" customHeight="1"/>
-    <row r="38" ht="17.25" customHeight="1"/>
-    <row r="39" ht="17.25" customHeight="1"/>
-    <row r="40" ht="17.25" customHeight="1"/>
-    <row r="41" ht="17.25" customHeight="1"/>
-    <row r="42" ht="17.25" customHeight="1"/>
-    <row r="43" ht="17.25" customHeight="1"/>
-    <row r="44" ht="17.25" customHeight="1"/>
-    <row r="45" ht="17.25" customHeight="1"/>
-    <row r="46" ht="17.25" customHeight="1"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+    </row>
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+    </row>
+    <row r="17" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+    </row>
+    <row r="18" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+    </row>
+    <row r="19" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+    </row>
+    <row r="20" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+    </row>
+    <row r="21" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+    </row>
+    <row r="22" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+    </row>
+    <row r="23" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+    </row>
+    <row r="24" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+    </row>
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+    </row>
+    <row r="26" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+    </row>
+    <row r="27" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+    </row>
+    <row r="28" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+    </row>
+    <row r="29" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+    </row>
+    <row r="30" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+    </row>
+    <row r="31" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+    </row>
+    <row r="38" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+    </row>
+    <row r="39" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+    </row>
+    <row r="40" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+    </row>
+    <row r="41" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+    </row>
+    <row r="42" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+    </row>
+    <row r="43" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+    </row>
+    <row r="44" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+    </row>
+    <row r="45" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+    </row>
+    <row r="46" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010019714232D8671D41B688C3A48C5AE621" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d53d216ca0852b3df112c80684e44a04">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0590885-0391-4acc-a1a2-62bdd649afdc" xmlns:ns3="f203ef26-be28-437c-ae01-5f41441de6d3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a994f462a7971573747b1ee30b6f4c90" ns2:_="" ns3:_="">
+    <xsd:import namespace="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
+    <xsd:import namespace="f203ef26-be28-437c-ae01-5f41441de6d3"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0590885-0391-4acc-a1a2-62bdd649afdc" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2cfdae59-7532-4cc8-8ce8-63e07576e745" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f203ef26-be28-437c-ae01-5f41441de6d3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{af0a4373-ad75-4169-a61b-b6de68ac2aea}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f203ef26-be28-437c-ae01-5f41441de6d3">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="f203ef26-be28-437c-ae01-5f41441de6d3">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="f203ef26-be28-437c-ae01-5f41441de6d3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0590885-0391-4acc-a1a2-62bdd649afdc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C2D16A-6A14-4FCF-9B7F-81D5BCF9F508}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B1B1D8-E7B0-43D3-BF30-A53ECE29C72F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
+    <ds:schemaRef ds:uri="f203ef26-be28-437c-ae01-5f41441de6d3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56BCB5A8-855F-4A49-B3E4-B6B1DAD57931}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E58E092-0497-4CF3-8876-CC340FCDDFD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f203ef26-be28-437c-ae01-5f41441de6d3"/>
+    <ds:schemaRef ds:uri="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/excel_test_cases_updated/test_create_pr_copy.xlsx
+++ b/excel_test_cases_updated/test_create_pr_copy.xlsx
@@ -1,881 +1,180 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samit paudel\Downloads\ariba_automation\sap_test_automation\excel_test_cases\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="878" firstSheet="1" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="878" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario Cover Sheet" sheetId="15" r:id="rId1"/>
-    <sheet name="Steps" sheetId="17" r:id="rId2"/>
-    <sheet name="References" sheetId="18" r:id="rId3"/>
-    <sheet name="Scenario Metrics " sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Scenario Cover Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Steps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="References" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scenario Metrics " sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Steps!$A$1:$Q$14</definedName>
-  </definedNames>
-  <calcPr calcId="162913"/>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
-  <si>
-    <t xml:space="preserve">Scenario Owner: </t>
-  </si>
-  <si>
-    <t>Test Cycle:</t>
-  </si>
-  <si>
-    <t>Scenario ID:</t>
-  </si>
-  <si>
-    <t>GPO-001</t>
-  </si>
-  <si>
-    <t>Test Objective:</t>
-  </si>
-  <si>
-    <t>Create PR and PO in guided buying.</t>
-  </si>
-  <si>
-    <t>Scenario Description:</t>
-  </si>
-  <si>
-    <t>Long Description Scenario Summary for items to be tested</t>
-  </si>
-  <si>
-    <t>Search catalog for items
-Add items to cart
-Complete requisition details and submit
-Review PR approval flow 
-Confirm PO generation
-Create associated receipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Data Requirements</t>
-  </si>
-  <si>
-    <t>Legacy Reference</t>
-  </si>
-  <si>
-    <t>SAP Reference</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prerequisite </t>
-  </si>
-  <si>
-    <t>Key RICEF Objects</t>
-  </si>
-  <si>
-    <t>Master Data Validation</t>
-  </si>
-  <si>
-    <t>SAP PO Post and Validation</t>
-  </si>
-  <si>
-    <t>SAP Invoice to SAP</t>
-  </si>
-  <si>
-    <t>Payment Remitance Validation to Ariba</t>
-  </si>
-  <si>
-    <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Signature</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Scenario Number</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description </t>
-  </si>
-  <si>
-    <t>Test Data / Test Execution</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Step Completed
-Sucessfullyåç</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>FI Impact</t>
-  </si>
-  <si>
-    <t>RICEF Tested</t>
-  </si>
-  <si>
-    <t>TPR #</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Tester/User ID</t>
-  </si>
-  <si>
-    <t>Y or N</t>
-  </si>
-  <si>
-    <t>Scenario No.</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>BL_001</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Buyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login
-Password
-</t>
-  </si>
-  <si>
-    <t>Catalog</t>
-  </si>
-  <si>
-    <t>Desired quantity is indicated.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Press</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Cart</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" button.</t>
-    </r>
-  </si>
-  <si>
-    <t>Shopping Cart popup  window appears.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-  </si>
-  <si>
-    <t>Requisition screen appears. The system assigns the PR number to the document.</t>
-  </si>
-  <si>
-    <t>Requisition Header</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Enter the requistion title on "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Requistion title</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" box.</t>
-    </r>
-  </si>
-  <si>
-    <t>Requisition title is updated.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Enter or verify the remaing data elements on the Requistion screen.
-Note: Only "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">red </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" items should be editable.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Fields are updated without any error.</t>
-  </si>
-  <si>
-    <t>Need-by is Today +5</t>
-  </si>
-  <si>
-    <t>Requisition Lines</t>
-  </si>
-  <si>
-    <t>Fields are updated</t>
-  </si>
-  <si>
-    <t>Requisition</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Press "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Submit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"  to submit the requisition for approval. </t>
-    </r>
-  </si>
-  <si>
-    <t>Message appears "Your requisition has been sent for approval.</t>
-  </si>
-  <si>
-    <t>View Approval Flow</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Click on </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Requisition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to display the created requisiton. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Submitted</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The PR is now on Submitted status.
-Approval Flow is now active shown by </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>green flow.</t>
-    </r>
-  </si>
-  <si>
-    <t>Count of Status</t>
-  </si>
-  <si>
-    <t>(blank)</t>
-  </si>
-  <si>
-    <t>10 - Not Started</t>
-  </si>
-  <si>
-    <t>20 - In-Process</t>
-  </si>
-  <si>
-    <t>30 - TPR Hold</t>
-  </si>
-  <si>
-    <t>40 - DEV Hold</t>
-  </si>
-  <si>
-    <t>50 - Pass</t>
-  </si>
-  <si>
-    <t>60 - N/A</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>PP_018</t>
-  </si>
-  <si>
-    <t>RTR</t>
-  </si>
-  <si>
-    <t>PTP</t>
-  </si>
-  <si>
-    <t>PP</t>
-  </si>
-  <si>
-    <t>IMWM</t>
-  </si>
-  <si>
-    <t>PP_018 Total</t>
-  </si>
-  <si>
-    <t>ZZZ999</t>
-  </si>
-  <si>
-    <t>ZZZ999 Total</t>
-  </si>
-  <si>
-    <t>Complete script GEN-002 to log into Ariba "Advanced" Buying and Invoicing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexus Water Group homepage is presented. </t>
-  </si>
-  <si>
-    <t>Click on Catalog Tab</t>
-  </si>
-  <si>
-    <t>Catalog page is displayed</t>
-  </si>
-  <si>
-    <t>On the search bar where it says "Search by part #, supplier name or keyword", type in the item you want to purchase.</t>
-  </si>
-  <si>
-    <t>Book Bins - Set of 12</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>From the search result, find the item. Enter the desired quantity  in the "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Qty</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> box.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quantity :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen. Click on Proceed to Checkout button.
-</t>
-  </si>
-  <si>
-    <t>AT-1</t>
-  </si>
-  <si>
-    <r>
-      <t>Click on the</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkbox</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the line for the item (towards the item lines' top left).
-Click on </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Actions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dropdown and then </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Edit Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Edit Detail page for the item is displayed.</t>
-  </si>
-  <si>
-    <r>
-      <t>Scroll down to Accounting - by Line Item Section</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Enter or  verify the information in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Accounting  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">section. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Enter or  verify the information in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Shipping - by Line Item </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>section.</t>
-    </r>
-  </si>
-  <si>
-    <t>Enter or verify the Line Item Details for the item.
-(Most details in this section is set to default)</t>
-  </si>
-  <si>
-    <t>Fields are validated and updated if necessary.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="25">
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="8"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="12"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="14"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF0070C0"/>
       <sz val="14"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF00B050"/>
       <sz val="14"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="14"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FFFF0000"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF00B0F0"/>
       <sz val="14"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF262626"/>
       <sz val="14"/>
-      <color rgb="FF262626"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF00B050"/>
       <sz val="16"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF0070C0"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF00B0F0"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -917,7 +216,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -1497,316 +796,413 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="142">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" pivotButton="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="1" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="1" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1996,58 +1392,58 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
@@ -2100,56 +1496,22 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF00B0F0"/>
-      <color rgb="FFE2EFDA"/>
-      <color rgb="FFCEE4CB"/>
-      <color rgb="FFFDE9D9"/>
-      <color rgb="FFE4DFEC"/>
-      <color rgb="FFDDEBF7"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Browning G Hollomon" refreshedDate="39386.436179745368" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1">
+<pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" refreshedBy="Browning G Hollomon" refreshedDate="39386.43617974537" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1" r:id="rId1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final" r:id="rId2"/>
+    <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final"/>
   </cacheSource>
   <cacheFields count="15">
-    <cacheField name="Scenario Number" numFmtId="0">
-      <sharedItems containsBlank="1" count="28">
+    <cacheField name="Scenario Number" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="28" containsBlank="1">
         <m/>
         <s v="Demand Planning"/>
         <s v="FTS001"/>
@@ -2180,11 +1542,11 @@
         <s v="OTC001" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Step" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="46"/>
+    <cacheField name="Step" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1" containsInteger="1" containsNumber="1" containsString="0" minValue="1" maxValue="46"/>
     </cacheField>
-    <cacheField name="Team" numFmtId="0">
-      <sharedItems containsBlank="1" count="7">
+    <cacheField name="Team" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="7" containsBlank="1">
         <m/>
         <s v="FTS"/>
         <s v="PTP"/>
@@ -2194,35 +1556,35 @@
         <s v="XXX" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Description " numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="Description " uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tcode" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="Tcode" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tester" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="Tester" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Test Data / Test Execution" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="Test Data / Test Execution" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Expected Result" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="Expected Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Actual Result" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="Actual Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="FI Impact" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="FI Impact" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="RICEF Tested" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+    <cacheField name="RICEF Tested" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="TPR #" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    <cacheField name="TPR #" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
     </cacheField>
-    <cacheField name="Status" numFmtId="0">
-      <sharedItems containsBlank="1" count="34">
+    <cacheField name="Status" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="34" containsBlank="1">
         <m/>
         <s v="50 - Pass"/>
         <s v="60 - N/A"/>
@@ -2259,23 +1621,18 @@
         <s v="20 In Process" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="User ID" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    <cacheField name="User ID" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
     </cacheField>
-    <cacheField name="Comments" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    <cacheField name="Comments" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
     </cacheField>
   </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="137">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137">
   <r>
     <x v="0"/>
     <m/>
@@ -4609,231 +3966,231 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" dataCaption="Data" showError="0" showMissing="1" updatedVersion="3" minRefreshableVersion="0" asteriskTotals="0" showItems="1" editData="0" disableFieldList="0" showCalcMbrs="1" visualTotals="1" showMultipleLabel="1" showDataDropDown="1" showDrill="1" printDrill="0" showMemberPropertyTips="0" showDataTips="1" enableWizard="1" enableDrill="1" enableFieldProperties="1" preserveFormatting="1" useAutoFormatting="1" pageWrap="0" pageOverThenDown="0" subtotalHiddenItems="0" rowGrandTotals="1" colGrandTotals="1" fieldPrintTitles="0" itemPrintTitles="1" mergeItem="0" showDropZones="1" createdVersion="1" indent="0" showEmptyRow="0" showEmptyCol="0" showHeaders="1" compact="0" outline="0" outlineData="0" compactData="0" published="0" gridDropZones="1" immersive="1" multipleFieldFilters="0" chartFormat="0" fieldListSortAscending="0" mdxSubqueries="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" r:id="rId1">
   <location ref="A3:J12" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="15">
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
+    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
       <items count="29">
-        <item h="1" m="1" x="27"/>
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="10"/>
-        <item n="PP_018" x="2"/>
-        <item m="1" x="8"/>
-        <item x="7"/>
-        <item m="1" x="16"/>
-        <item m="1" x="18"/>
-        <item m="1" x="20"/>
-        <item m="1" x="22"/>
-        <item m="1" x="23"/>
-        <item m="1" x="24"/>
-        <item m="1" x="25"/>
-        <item m="1" x="26"/>
-        <item m="1" x="9"/>
-        <item m="1" x="11"/>
-        <item m="1" x="12"/>
-        <item m="1" x="13"/>
-        <item m="1" x="14"/>
-        <item m="1" x="15"/>
-        <item m="1" x="17"/>
-        <item m="1" x="19"/>
-        <item m="1" x="21"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
+        <item t="data" h="1" sd="1" m="1" x="27"/>
+        <item t="data" h="1" sd="1" x="0"/>
+        <item t="data" h="1" sd="1" m="1" x="10"/>
+        <item n="PP_018" t="data" sd="1" x="2"/>
+        <item t="data" sd="1" m="1" x="8"/>
+        <item t="data" sd="1" x="7"/>
+        <item t="data" sd="1" m="1" x="16"/>
+        <item t="data" sd="1" m="1" x="18"/>
+        <item t="data" sd="1" m="1" x="20"/>
+        <item t="data" sd="1" m="1" x="22"/>
+        <item t="data" sd="1" m="1" x="23"/>
+        <item t="data" sd="1" m="1" x="24"/>
+        <item t="data" sd="1" m="1" x="25"/>
+        <item t="data" sd="1" m="1" x="26"/>
+        <item t="data" sd="1" m="1" x="9"/>
+        <item t="data" sd="1" m="1" x="11"/>
+        <item t="data" sd="1" m="1" x="12"/>
+        <item t="data" sd="1" m="1" x="13"/>
+        <item t="data" sd="1" m="1" x="14"/>
+        <item t="data" sd="1" m="1" x="15"/>
+        <item t="data" sd="1" m="1" x="17"/>
+        <item t="data" sd="1" m="1" x="19"/>
+        <item t="data" sd="1" m="1" x="21"/>
+        <item t="data" sd="1" x="1"/>
+        <item t="data" sd="1" x="3"/>
+        <item t="data" sd="1" x="4"/>
+        <item t="data" sd="1" x="5"/>
+        <item t="data" sd="1" x="6"/>
+        <item t="default" sd="1"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
       <items count="8">
-        <item h="1" x="0"/>
-        <item m="1" x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item n="PP" x="1"/>
-        <item m="1" x="6"/>
-        <item x="3"/>
-        <item t="default"/>
+        <item t="data" h="1" sd="1" x="0"/>
+        <item t="data" sd="1" m="1" x="5"/>
+        <item t="data" sd="1" x="4"/>
+        <item t="data" sd="1" x="2"/>
+        <item n="PP" t="data" sd="1" x="1"/>
+        <item t="data" sd="1" m="1" x="6"/>
+        <item t="data" sd="1" x="3"/>
+        <item t="default" sd="1"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField axis="axisCol" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField axis="axisCol" dataField="1" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
       <items count="35">
-        <item m="1" x="12"/>
-        <item m="1" x="16"/>
-        <item m="1" x="29"/>
-        <item m="1" x="31"/>
-        <item m="1" x="24"/>
-        <item x="0"/>
-        <item m="1" x="17"/>
-        <item m="1" x="33"/>
-        <item m="1" x="26"/>
-        <item m="1" x="13"/>
-        <item m="1" x="9"/>
-        <item m="1" x="25"/>
-        <item m="1" x="8"/>
-        <item m="1" x="28"/>
-        <item m="1" x="19"/>
-        <item m="1" x="30"/>
-        <item m="1" x="15"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item m="1" x="10"/>
-        <item m="1" x="18"/>
-        <item m="1" x="11"/>
-        <item m="1" x="22"/>
-        <item m="1" x="32"/>
-        <item m="1" x="20"/>
-        <item m="1" x="27"/>
-        <item m="1" x="14"/>
-        <item m="1" x="23"/>
-        <item m="1" x="7"/>
-        <item m="1" x="21"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
+        <item t="data" sd="1" m="1" x="12"/>
+        <item t="data" sd="1" m="1" x="16"/>
+        <item t="data" sd="1" m="1" x="29"/>
+        <item t="data" sd="1" m="1" x="31"/>
+        <item t="data" sd="1" m="1" x="24"/>
+        <item t="data" sd="1" x="0"/>
+        <item t="data" sd="1" m="1" x="17"/>
+        <item t="data" sd="1" m="1" x="33"/>
+        <item t="data" sd="1" m="1" x="26"/>
+        <item t="data" sd="1" m="1" x="13"/>
+        <item t="data" sd="1" m="1" x="9"/>
+        <item t="data" sd="1" m="1" x="25"/>
+        <item t="data" sd="1" m="1" x="8"/>
+        <item t="data" sd="1" m="1" x="28"/>
+        <item t="data" sd="1" m="1" x="19"/>
+        <item t="data" sd="1" m="1" x="30"/>
+        <item t="data" sd="1" m="1" x="15"/>
+        <item t="data" sd="1" x="3"/>
+        <item t="data" sd="1" x="4"/>
+        <item t="data" sd="1" x="5"/>
+        <item t="data" sd="1" x="6"/>
+        <item t="data" sd="1" m="1" x="10"/>
+        <item t="data" sd="1" m="1" x="18"/>
+        <item t="data" sd="1" m="1" x="11"/>
+        <item t="data" sd="1" m="1" x="22"/>
+        <item t="data" sd="1" m="1" x="32"/>
+        <item t="data" sd="1" m="1" x="20"/>
+        <item t="data" sd="1" m="1" x="27"/>
+        <item t="data" sd="1" m="1" x="14"/>
+        <item t="data" sd="1" m="1" x="23"/>
+        <item t="data" sd="1" m="1" x="7"/>
+        <item t="data" sd="1" m="1" x="21"/>
+        <item t="data" sd="1" x="1"/>
+        <item t="data" sd="1" x="2"/>
+        <item t="default" sd="1"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
     <field x="2"/>
   </rowFields>
   <rowItems count="8">
-    <i>
+    <i t="data" r="0" i="0">
       <x v="3"/>
       <x v="2"/>
     </i>
-    <i r="1">
+    <i t="data" r="1" i="0">
       <x v="3"/>
     </i>
-    <i r="1">
+    <i t="data" r="1" i="0">
       <x v="4"/>
     </i>
-    <i r="1">
+    <i t="data" r="1" i="0">
       <x v="6"/>
     </i>
-    <i t="default">
+    <i t="default" r="0" i="0">
       <x v="3"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="5"/>
       <x v="4"/>
     </i>
-    <i t="default">
+    <i t="default" r="0" i="0">
       <x v="5"/>
     </i>
-    <i t="grand">
-      <x/>
+    <i t="grand" r="0" i="0">
+      <x v="0"/>
     </i>
   </rowItems>
   <colFields count="1">
     <field x="12"/>
   </colFields>
   <colItems count="8">
-    <i>
+    <i t="data" r="0" i="0">
       <x v="5"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="17"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="18"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="19"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="20"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="32"/>
     </i>
-    <i>
+    <i t="data" r="0" i="0">
       <x v="33"/>
     </i>
-    <i t="grand">
-      <x/>
+    <i t="grand" r="0" i="0">
+      <x v="0"/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Status" fld="12" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Count of Status" fld="12" subtotal="count" showDataAs="normal" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="44">
-    <format dxfId="43">
-      <pivotArea outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="43">
+      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format action="formatting" dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format action="formatting" dxfId="41">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="40">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="40">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="0"/>
+          <reference field="2"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="39">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format action="formatting" dxfId="38">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="37">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
-      <pivotArea outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="36">
+      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format action="formatting" dxfId="35">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format action="formatting" dxfId="34">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="33">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="33">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="0"/>
+          <reference field="2"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="32">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="31">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="30">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format action="formatting" dxfId="29">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format action="formatting" dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="27">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" count="5">
+          <reference field="12">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4843,10 +4200,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
-      <pivotArea outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="26">
+      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" count="5" selected="0">
+          <reference field="12" selected="0">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4856,16 +4213,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format action="formatting" dxfId="25">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format action="formatting" dxfId="24">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="23">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" count="5">
+          <reference field="12">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4875,181 +4232,176 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="22">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1">
+          <reference field="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="21">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" defaultSubtotal="1">
+          <reference field="0" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="20">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" count="1" selected="0">
+          <reference field="0" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="2" count="0"/>
+          <reference field="2"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="19">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1">
+          <reference field="0">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="18">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" defaultSubtotal="1">
+          <reference field="0" defaultSubtotal="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="17">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" count="1" selected="0">
+          <reference field="0" selected="0">
             <x v="2"/>
           </reference>
-          <reference field="2" count="1">
+          <reference field="2">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format action="formatting" dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
-      <pivotArea outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="15">
+      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" selected="0" defaultSubtotal="1">
+          <reference field="0" selected="0" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="14">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" defaultSubtotal="1">
+          <reference field="0" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
-      <pivotArea outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="13">
+      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" selected="0" defaultSubtotal="1">
+          <reference field="0" selected="0" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
-      <pivotArea outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="12">
+      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" selected="0">
+          <reference field="0" selected="0">
             <x v="5"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format action="formatting" dxfId="11">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format action="formatting" dxfId="10">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format action="formatting" dxfId="9">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="8">
+    <format action="formatting" dxfId="8">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format action="formatting" dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="6">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="0"/>
+          <reference field="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="5">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" defaultSubtotal="1">
+          <reference field="0" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="4">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" count="1" selected="0">
+          <reference field="0" selected="0">
             <x v="3"/>
           </reference>
-          <reference field="2" count="0"/>
+          <reference field="2"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="3">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" count="1" selected="0">
+          <reference field="0" selected="0">
             <x v="5"/>
           </reference>
-          <reference field="2" count="2">
+          <reference field="2">
             <x v="4"/>
             <x v="6"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format action="formatting" dxfId="2">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="1">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" count="0"/>
+          <reference field="12"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format action="formatting" dxfId="0">
+      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" count="0"/>
+          <reference field="12"/>
         </references>
       </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
 </pivotTableDefinition>
 </file>
 
@@ -5339,2482 +4691,1706 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="2" width="25.88671875" style="38" customWidth="1"/>
-    <col min="3" max="3" width="25" style="38" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" style="38" customWidth="1"/>
-    <col min="6" max="14" width="40.88671875" style="38" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="38"/>
+    <col width="25.88671875" customWidth="1" style="38" min="1" max="2"/>
+    <col width="25" customWidth="1" style="38" min="3" max="3"/>
+    <col width="25.88671875" customWidth="1" style="38" min="4" max="4"/>
+    <col width="34.88671875" customWidth="1" style="38" min="5" max="5"/>
+    <col width="40.88671875" customWidth="1" style="38" min="6" max="14"/>
+    <col width="9.109375" customWidth="1" style="38" min="15" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-    </row>
-    <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="98" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="100"/>
-    </row>
-    <row r="4" spans="1:6" ht="12" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="100"/>
-    </row>
-    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="101" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="103"/>
-    </row>
-    <row r="6" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="105"/>
-    </row>
-    <row r="7" spans="1:6" ht="12" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42"/>
-      <c r="E7" s="43"/>
-    </row>
-    <row r="8" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="106" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="108"/>
-    </row>
-    <row r="9" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-    </row>
-    <row r="10" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="112"/>
-      <c r="B10" s="113"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="114"/>
-    </row>
-    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114"/>
-    </row>
-    <row r="12" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="112"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="112"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="114"/>
-    </row>
-    <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="112"/>
-      <c r="B14" s="113"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="114"/>
-    </row>
-    <row r="15" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="112"/>
-      <c r="B15" s="113"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="114"/>
-    </row>
-    <row r="16" spans="1:6" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="46"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="69"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="116"/>
-    </row>
-    <row r="18" spans="1:5" ht="12" x14ac:dyDescent="0.25">
-      <c r="A18" s="67"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="118"/>
-    </row>
-    <row r="19" spans="1:5" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="68"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="118"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="118"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="50"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="118"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="47"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="118"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="118"/>
-    </row>
-    <row r="24" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="51"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="118"/>
-    </row>
-    <row r="25" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="46"/>
-    </row>
-    <row r="26" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="94"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="43"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="94"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="43"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="94"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="43"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="94"/>
-      <c r="B29" s="95"/>
-      <c r="C29" s="95"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="43"/>
-    </row>
-    <row r="30" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
-      <c r="E30" s="43"/>
-    </row>
-    <row r="31" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="46"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="94" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="95"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="43"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="94" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="95"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="43"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="94" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="95"/>
-      <c r="C34" s="95"/>
-      <c r="D34" s="95"/>
-      <c r="E34" s="43"/>
-    </row>
-    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="95"/>
-      <c r="C35" s="95"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="52"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="117"/>
-      <c r="B36" s="119"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="43"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="117"/>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="43"/>
-    </row>
-    <row r="38" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="43"/>
-    </row>
-    <row r="39" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="46"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="56"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="58"/>
-    </row>
-    <row r="41" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59"/>
-      <c r="B41" s="60"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
-    </row>
-    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="62"/>
-      <c r="B47" s="63"/>
-      <c r="C47" s="63"/>
-      <c r="D47" s="63"/>
-    </row>
-    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="62"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="63"/>
-      <c r="D48" s="63"/>
-    </row>
-    <row r="49" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A49" s="64"/>
-      <c r="B49" s="65"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="65"/>
-      <c r="E49" s="65"/>
-    </row>
-    <row r="50" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A50" s="63"/>
-      <c r="B50" s="63"/>
-      <c r="C50" s="63"/>
-      <c r="D50" s="63"/>
-    </row>
-    <row r="51" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A51" s="63"/>
-      <c r="B51" s="63"/>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-    </row>
-    <row r="52" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A52" s="63"/>
-      <c r="B52" s="63"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-    </row>
-    <row r="53" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A53" s="63"/>
-      <c r="B53" s="63"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="63"/>
-    </row>
-    <row r="54" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A54" s="63"/>
-      <c r="B54" s="63"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="63"/>
-    </row>
-    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="62"/>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-    </row>
-    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="62"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-    </row>
-    <row r="57" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A57" s="63"/>
-      <c r="B57" s="63"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="63"/>
-      <c r="E57" s="63"/>
-    </row>
-    <row r="58" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A58" s="63"/>
-      <c r="B58" s="63"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="63"/>
-      <c r="E58" s="63"/>
-    </row>
-    <row r="59" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A59" s="63"/>
-      <c r="B59" s="63"/>
-      <c r="C59" s="63"/>
-      <c r="D59" s="63"/>
-      <c r="E59" s="63"/>
-    </row>
-    <row r="60" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A60" s="63"/>
-      <c r="B60" s="63"/>
-      <c r="C60" s="63"/>
-      <c r="D60" s="63"/>
-      <c r="E60" s="63"/>
-    </row>
-    <row r="61" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A61" s="63"/>
-      <c r="B61" s="63"/>
-      <c r="C61" s="63"/>
-      <c r="D61" s="63"/>
-      <c r="E61" s="63"/>
-    </row>
-    <row r="62" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A62" s="63"/>
-      <c r="B62" s="63"/>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-    </row>
-    <row r="63" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A63" s="63"/>
-      <c r="B63" s="63"/>
-      <c r="C63" s="63"/>
-      <c r="D63" s="63"/>
-      <c r="E63" s="63"/>
-    </row>
-    <row r="64" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A64" s="63"/>
-      <c r="B64" s="63"/>
-      <c r="C64" s="63"/>
-      <c r="D64" s="63"/>
-      <c r="E64" s="63"/>
-    </row>
-    <row r="65" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A65" s="63"/>
-      <c r="B65" s="63"/>
-      <c r="C65" s="63"/>
-      <c r="D65" s="63"/>
-      <c r="E65" s="63"/>
-    </row>
-    <row r="66" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A66" s="63"/>
-      <c r="B66" s="63"/>
-      <c r="C66" s="63"/>
-      <c r="D66" s="63"/>
-      <c r="E66" s="63"/>
-    </row>
-    <row r="67" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A67" s="63"/>
-      <c r="B67" s="63"/>
-      <c r="C67" s="63"/>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-    </row>
-    <row r="68" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A68" s="63"/>
-      <c r="B68" s="63"/>
-      <c r="C68" s="63"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="63"/>
-    </row>
-    <row r="69" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A69" s="63"/>
-      <c r="B69" s="63"/>
-      <c r="C69" s="63"/>
-      <c r="D69" s="63"/>
-      <c r="E69" s="63"/>
-    </row>
-    <row r="70" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A70" s="63"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="63"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="63"/>
+    <row r="1" ht="14.1" customHeight="1" thickBot="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scenario Owner: </t>
+        </is>
+      </c>
+      <c r="B1" s="35" t="n"/>
+      <c r="C1" s="36" t="n"/>
+      <c r="D1" s="36" t="n"/>
+      <c r="E1" s="37" t="n"/>
+    </row>
+    <row r="2" ht="14.1" customHeight="1" thickBot="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Test Cycle:</t>
+        </is>
+      </c>
+      <c r="B2" s="96" t="n"/>
+      <c r="C2" s="123" t="n"/>
+      <c r="D2" s="97" t="n"/>
+      <c r="E2" s="41" t="n"/>
+    </row>
+    <row r="3" ht="12" customHeight="1">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>Scenario ID:</t>
+        </is>
+      </c>
+      <c r="B3" s="124" t="inlineStr">
+        <is>
+          <t>GPO-001</t>
+        </is>
+      </c>
+      <c r="C3" s="125" t="n"/>
+      <c r="D3" s="125" t="n"/>
+      <c r="E3" s="126" t="n"/>
+    </row>
+    <row r="4" ht="12" customHeight="1">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>Test Objective:</t>
+        </is>
+      </c>
+      <c r="B4" s="124" t="inlineStr">
+        <is>
+          <t>Create PR and PO in guided buying.</t>
+        </is>
+      </c>
+      <c r="C4" s="125" t="n"/>
+      <c r="D4" s="125" t="n"/>
+      <c r="E4" s="126" t="n"/>
+    </row>
+    <row r="5" ht="12" customHeight="1">
+      <c r="A5" s="127" t="inlineStr">
+        <is>
+          <t>Scenario Description:</t>
+        </is>
+      </c>
+      <c r="B5" s="105" t="n"/>
+      <c r="E5" s="128" t="n"/>
+    </row>
+    <row r="6" ht="14.1" customHeight="1" thickBot="1">
+      <c r="A6" s="129" t="n"/>
+      <c r="B6" s="130" t="n"/>
+      <c r="C6" s="130" t="n"/>
+      <c r="D6" s="130" t="n"/>
+      <c r="E6" s="131" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1" thickBot="1">
+      <c r="A7" s="42" t="n"/>
+      <c r="E7" s="43" t="n"/>
+    </row>
+    <row r="8" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A8" s="127" t="inlineStr">
+        <is>
+          <t>Long Description Scenario Summary for items to be tested</t>
+        </is>
+      </c>
+      <c r="B8" s="132" t="n"/>
+      <c r="C8" s="132" t="n"/>
+      <c r="D8" s="132" t="n"/>
+      <c r="E8" s="133" t="n"/>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="134" t="inlineStr">
+        <is>
+          <t>Search catalog for items
+Add items to cart
+Complete requisition details and submit
+Review PR approval flow 
+Confirm PO generation
+Create associated receipt</t>
+        </is>
+      </c>
+      <c r="B9" s="135" t="n"/>
+      <c r="C9" s="135" t="n"/>
+      <c r="D9" s="135" t="n"/>
+      <c r="E9" s="136" t="n"/>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="137" t="n"/>
+      <c r="E10" s="128" t="n"/>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="137" t="n"/>
+      <c r="E11" s="128" t="n"/>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="137" t="n"/>
+      <c r="E12" s="128" t="n"/>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="137" t="n"/>
+      <c r="E13" s="128" t="n"/>
+    </row>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="A14" s="137" t="n"/>
+      <c r="E14" s="128" t="n"/>
+    </row>
+    <row r="15" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A15" s="137" t="n"/>
+      <c r="E15" s="128" t="n"/>
+    </row>
+    <row r="16" ht="12.6" customHeight="1" thickBot="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>Data Requirements</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Legacy Reference</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>SAP Reference</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="69" t="n"/>
+      <c r="B17" s="113" t="n"/>
+      <c r="C17" s="95" t="n"/>
+      <c r="D17" s="138" t="n"/>
+      <c r="E17" s="136" t="n"/>
+    </row>
+    <row r="18" ht="12" customHeight="1">
+      <c r="A18" s="67" t="n"/>
+      <c r="B18" s="95" t="n"/>
+      <c r="C18" s="95" t="n"/>
+      <c r="D18" s="137" t="n"/>
+      <c r="E18" s="128" t="n"/>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="A19" s="68" t="n"/>
+      <c r="B19" s="95" t="n"/>
+      <c r="C19" s="95" t="n"/>
+      <c r="D19" s="137" t="n"/>
+      <c r="E19" s="128" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="95" t="n"/>
+      <c r="C20" s="95" t="n"/>
+      <c r="D20" s="137" t="n"/>
+      <c r="E20" s="128" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="95" t="n"/>
+      <c r="D21" s="137" t="n"/>
+      <c r="E21" s="128" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="112" t="n"/>
+      <c r="B22" s="113" t="n"/>
+      <c r="C22" s="95" t="n"/>
+      <c r="D22" s="137" t="n"/>
+      <c r="E22" s="128" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="112" t="n"/>
+      <c r="B23" s="113" t="n"/>
+      <c r="C23" s="95" t="n"/>
+      <c r="D23" s="137" t="n"/>
+      <c r="E23" s="128" t="n"/>
+    </row>
+    <row r="24" ht="12" customHeight="1" thickBot="1">
+      <c r="A24" s="51" t="n"/>
+      <c r="D24" s="137" t="n"/>
+      <c r="E24" s="128" t="n"/>
+    </row>
+    <row r="25" ht="12.6" customHeight="1" thickBot="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prerequisite </t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n"/>
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="46" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" s="94" t="n"/>
+      <c r="E26" s="43" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="94" t="n"/>
+      <c r="E27" s="43" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="94" t="n"/>
+      <c r="E28" s="43" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="94" t="n"/>
+      <c r="E29" s="43" t="n"/>
+    </row>
+    <row r="30" ht="12" customHeight="1" thickBot="1">
+      <c r="A30" s="51" t="n"/>
+      <c r="E30" s="43" t="n"/>
+    </row>
+    <row r="31" ht="12.6" customHeight="1" thickBot="1">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>Key RICEF Objects</t>
+        </is>
+      </c>
+      <c r="B31" s="45" t="n"/>
+      <c r="C31" s="45" t="n"/>
+      <c r="D31" s="45" t="n"/>
+      <c r="E31" s="46" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="94" t="inlineStr">
+        <is>
+          <t>Master Data Validation</t>
+        </is>
+      </c>
+      <c r="E32" s="43" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="94" t="inlineStr">
+        <is>
+          <t>SAP PO Post and Validation</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="94" t="inlineStr">
+        <is>
+          <t>SAP Invoice to SAP</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="n"/>
+    </row>
+    <row r="35" ht="12.75" customHeight="1">
+      <c r="A35" s="94" t="inlineStr">
+        <is>
+          <t>Payment Remitance Validation to Ariba</t>
+        </is>
+      </c>
+      <c r="E35" s="52" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="117" t="n"/>
+      <c r="C36" s="119" t="n"/>
+      <c r="E36" s="43" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="117" t="n"/>
+      <c r="C37" s="119" t="n"/>
+      <c r="E37" s="43" t="n"/>
+    </row>
+    <row r="38" ht="12" customHeight="1" thickBot="1">
+      <c r="A38" s="53" t="inlineStr">
+        <is>
+          <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="n"/>
+    </row>
+    <row r="39" ht="12.6" customHeight="1" thickBot="1">
+      <c r="A39" s="54" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C39" s="55" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D39" s="55" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="109" t="n"/>
+      <c r="B40" s="110" t="n"/>
+      <c r="C40" s="110" t="n"/>
+      <c r="D40" s="110" t="n"/>
+      <c r="E40" s="58" t="n"/>
+    </row>
+    <row r="41" ht="12.6" customHeight="1" thickBot="1">
+      <c r="A41" s="59" t="n"/>
+      <c r="B41" s="60" t="n"/>
+      <c r="C41" s="60" t="n"/>
+      <c r="D41" s="60" t="n"/>
+      <c r="E41" s="61" t="n"/>
+    </row>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12" customHeight="1"/>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="63" t="n"/>
+      <c r="C47" s="63" t="n"/>
+      <c r="D47" s="63" t="n"/>
+    </row>
+    <row r="48" ht="12.75" customHeight="1">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="63" t="n"/>
+      <c r="C48" s="63" t="n"/>
+      <c r="D48" s="63" t="n"/>
+    </row>
+    <row r="49" ht="13.2" customHeight="1">
+      <c r="A49" s="64" t="n"/>
+      <c r="B49" s="65" t="n"/>
+      <c r="C49" s="66" t="n"/>
+      <c r="D49" s="65" t="n"/>
+      <c r="E49" s="65" t="n"/>
+    </row>
+    <row r="50" ht="13.2" customHeight="1">
+      <c r="A50" s="63" t="n"/>
+      <c r="B50" s="63" t="n"/>
+      <c r="C50" s="63" t="n"/>
+      <c r="D50" s="63" t="n"/>
+    </row>
+    <row r="51" ht="13.2" customHeight="1">
+      <c r="A51" s="63" t="n"/>
+      <c r="B51" s="63" t="n"/>
+      <c r="C51" s="63" t="n"/>
+      <c r="D51" s="63" t="n"/>
+    </row>
+    <row r="52" ht="13.2" customHeight="1">
+      <c r="A52" s="63" t="n"/>
+      <c r="B52" s="63" t="n"/>
+      <c r="C52" s="63" t="n"/>
+      <c r="D52" s="63" t="n"/>
+    </row>
+    <row r="53" ht="13.2" customHeight="1">
+      <c r="A53" s="63" t="n"/>
+      <c r="B53" s="63" t="n"/>
+      <c r="C53" s="63" t="n"/>
+      <c r="D53" s="63" t="n"/>
+    </row>
+    <row r="54" ht="13.2" customHeight="1">
+      <c r="A54" s="63" t="n"/>
+      <c r="B54" s="63" t="n"/>
+      <c r="C54" s="63" t="n"/>
+      <c r="D54" s="63" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="62" t="n"/>
+      <c r="B55" s="63" t="n"/>
+      <c r="C55" s="63" t="n"/>
+      <c r="D55" s="63" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="62" t="n"/>
+      <c r="B56" s="63" t="n"/>
+      <c r="C56" s="63" t="n"/>
+      <c r="D56" s="63" t="n"/>
+    </row>
+    <row r="57" ht="13.2" customHeight="1">
+      <c r="A57" s="63" t="n"/>
+      <c r="B57" s="63" t="n"/>
+      <c r="C57" s="63" t="n"/>
+      <c r="D57" s="63" t="n"/>
+      <c r="E57" s="63" t="n"/>
+    </row>
+    <row r="58" ht="13.2" customHeight="1">
+      <c r="A58" s="63" t="n"/>
+      <c r="B58" s="63" t="n"/>
+      <c r="C58" s="63" t="n"/>
+      <c r="D58" s="63" t="n"/>
+      <c r="E58" s="63" t="n"/>
+    </row>
+    <row r="59" ht="13.2" customHeight="1">
+      <c r="A59" s="63" t="n"/>
+      <c r="B59" s="63" t="n"/>
+      <c r="C59" s="63" t="n"/>
+      <c r="D59" s="63" t="n"/>
+      <c r="E59" s="63" t="n"/>
+    </row>
+    <row r="60" ht="13.2" customHeight="1">
+      <c r="A60" s="63" t="n"/>
+      <c r="B60" s="63" t="n"/>
+      <c r="C60" s="63" t="n"/>
+      <c r="D60" s="63" t="n"/>
+      <c r="E60" s="63" t="n"/>
+    </row>
+    <row r="61" ht="13.2" customHeight="1">
+      <c r="A61" s="63" t="n"/>
+      <c r="B61" s="63" t="n"/>
+      <c r="C61" s="63" t="n"/>
+      <c r="D61" s="63" t="n"/>
+      <c r="E61" s="63" t="n"/>
+    </row>
+    <row r="62" ht="13.2" customHeight="1">
+      <c r="A62" s="63" t="n"/>
+      <c r="B62" s="63" t="n"/>
+      <c r="C62" s="63" t="n"/>
+      <c r="D62" s="63" t="n"/>
+      <c r="E62" s="63" t="n"/>
+    </row>
+    <row r="63" ht="13.2" customHeight="1">
+      <c r="A63" s="63" t="n"/>
+      <c r="B63" s="63" t="n"/>
+      <c r="C63" s="63" t="n"/>
+      <c r="D63" s="63" t="n"/>
+      <c r="E63" s="63" t="n"/>
+    </row>
+    <row r="64" ht="13.2" customHeight="1">
+      <c r="A64" s="63" t="n"/>
+      <c r="B64" s="63" t="n"/>
+      <c r="C64" s="63" t="n"/>
+      <c r="D64" s="63" t="n"/>
+      <c r="E64" s="63" t="n"/>
+    </row>
+    <row r="65" ht="13.2" customHeight="1">
+      <c r="A65" s="63" t="n"/>
+      <c r="B65" s="63" t="n"/>
+      <c r="C65" s="63" t="n"/>
+      <c r="D65" s="63" t="n"/>
+      <c r="E65" s="63" t="n"/>
+    </row>
+    <row r="66" ht="13.2" customHeight="1">
+      <c r="A66" s="63" t="n"/>
+      <c r="B66" s="63" t="n"/>
+      <c r="C66" s="63" t="n"/>
+      <c r="D66" s="63" t="n"/>
+      <c r="E66" s="63" t="n"/>
+    </row>
+    <row r="67" ht="13.2" customHeight="1">
+      <c r="A67" s="63" t="n"/>
+      <c r="B67" s="63" t="n"/>
+      <c r="C67" s="63" t="n"/>
+      <c r="D67" s="63" t="n"/>
+      <c r="E67" s="63" t="n"/>
+    </row>
+    <row r="68" ht="13.2" customHeight="1">
+      <c r="A68" s="63" t="n"/>
+      <c r="B68" s="63" t="n"/>
+      <c r="C68" s="63" t="n"/>
+      <c r="D68" s="63" t="n"/>
+      <c r="E68" s="63" t="n"/>
+    </row>
+    <row r="69" ht="13.2" customHeight="1">
+      <c r="A69" s="63" t="n"/>
+      <c r="B69" s="63" t="n"/>
+      <c r="C69" s="63" t="n"/>
+      <c r="D69" s="63" t="n"/>
+      <c r="E69" s="63" t="n"/>
+    </row>
+    <row r="70" ht="13.2" customHeight="1">
+      <c r="A70" s="63" t="n"/>
+      <c r="B70" s="63" t="n"/>
+      <c r="C70" s="63" t="n"/>
+      <c r="D70" s="63" t="n"/>
+      <c r="E70" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:E6"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A9:E15"/>
     <mergeCell ref="D17:E24"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B5:E6"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E2">
+    <dataValidation sqref="D2:E2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"R4-Cycle 1,R4-Cycle 2,R4-Cycle 3,R4-Cycle 4,R4-Regression Test,R4-Business Simulation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="69" orientation="landscape" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageSetup orientation="landscape" scale="69"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultColWidth="35.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="35.6640625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="86" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="86" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="72" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="72" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="86" customWidth="1"/>
-    <col min="6" max="6" width="80.44140625" style="87" customWidth="1"/>
-    <col min="7" max="7" width="62.44140625" style="72" customWidth="1"/>
-    <col min="8" max="8" width="46.44140625" style="72" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" style="72" customWidth="1"/>
-    <col min="10" max="10" width="41.33203125" style="72" customWidth="1"/>
-    <col min="11" max="11" width="18.88671875" style="86" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" style="72" customWidth="1"/>
-    <col min="13" max="13" width="17.44140625" style="72" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="87" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" style="87" customWidth="1"/>
-    <col min="16" max="16" width="37.109375" style="72" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.109375" style="72"/>
-    <col min="18" max="16384" width="35.6640625" style="72"/>
+    <col width="10.33203125" customWidth="1" style="86" min="1" max="1"/>
+    <col width="18.6640625" customWidth="1" style="86" min="2" max="2"/>
+    <col width="10.33203125" customWidth="1" style="72" min="3" max="3"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="72" min="4" max="4"/>
+    <col width="14" customWidth="1" style="86" min="5" max="5"/>
+    <col width="80.44140625" customWidth="1" style="87" min="6" max="6"/>
+    <col width="62.44140625" customWidth="1" style="72" min="7" max="7"/>
+    <col width="46.44140625" customWidth="1" style="72" min="8" max="8"/>
+    <col width="15.88671875" customWidth="1" style="72" min="9" max="9"/>
+    <col width="41.33203125" customWidth="1" style="72" min="10" max="10"/>
+    <col width="18.88671875" customWidth="1" style="86" min="11" max="11"/>
+    <col width="18.6640625" customWidth="1" style="72" min="12" max="12"/>
+    <col width="17.44140625" customWidth="1" style="72" min="13" max="13"/>
+    <col width="16.44140625" customWidth="1" style="87" min="14" max="14"/>
+    <col width="13.33203125" customWidth="1" style="87" min="15" max="15"/>
+    <col width="37.109375" bestFit="1" customWidth="1" style="72" min="16" max="16"/>
+    <col width="9.109375" customWidth="1" style="72" min="17" max="17"/>
+    <col width="35.6640625" customWidth="1" style="72" min="18" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="120" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="71"/>
-      <c r="E1" s="120" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="120" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="121" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="120" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="120" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="120" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" s="120" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" s="120" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="120"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="73" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="120"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="74"/>
-    </row>
-    <row r="4" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="70" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="120" t="inlineStr">
+        <is>
+          <t>Scenario Number</t>
+        </is>
+      </c>
+      <c r="B1" s="120" t="n"/>
+      <c r="C1" s="120" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D1" s="120" t="n"/>
+      <c r="E1" s="120" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="F1" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description </t>
+        </is>
+      </c>
+      <c r="G1" s="120" t="inlineStr">
+        <is>
+          <t>Test Data / Test Execution</t>
+        </is>
+      </c>
+      <c r="H1" s="120" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="I1" s="121" t="inlineStr">
+        <is>
+          <t>Step Completed
+Sucessfullyåç</t>
+        </is>
+      </c>
+      <c r="J1" s="120" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="K1" s="120" t="inlineStr">
+        <is>
+          <t>FI Impact</t>
+        </is>
+      </c>
+      <c r="L1" s="120" t="inlineStr">
+        <is>
+          <t>RICEF Tested</t>
+        </is>
+      </c>
+      <c r="M1" s="120" t="inlineStr">
+        <is>
+          <t>TPR #</t>
+        </is>
+      </c>
+      <c r="N1" s="120" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O1" s="122" t="inlineStr">
+        <is>
+          <t>Tester/User ID</t>
+        </is>
+      </c>
+      <c r="P1" s="120" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="139" t="n"/>
+      <c r="B2" s="120" t="n"/>
+      <c r="C2" s="139" t="n"/>
+      <c r="D2" s="73" t="n"/>
+      <c r="E2" s="139" t="n"/>
+      <c r="F2" s="139" t="n"/>
+      <c r="G2" s="139" t="n"/>
+      <c r="H2" s="139" t="n"/>
+      <c r="I2" s="140" t="n"/>
+      <c r="J2" s="139" t="n"/>
+      <c r="K2" s="73" t="inlineStr">
+        <is>
+          <t>Y or N</t>
+        </is>
+      </c>
+      <c r="L2" s="139" t="n"/>
+      <c r="M2" s="139" t="n"/>
+      <c r="N2" s="139" t="n"/>
+      <c r="O2" s="141" t="n"/>
+      <c r="P2" s="139" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="74" t="n"/>
+      <c r="B3" s="74" t="inlineStr">
+        <is>
+          <t>Scenario No.</t>
+        </is>
+      </c>
+      <c r="C3" s="74" t="n"/>
+      <c r="D3" s="74" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="E3" s="74" t="n"/>
+      <c r="F3" s="75" t="n"/>
+      <c r="G3" s="76" t="n"/>
+      <c r="H3" s="76" t="n"/>
+      <c r="I3" s="76" t="n"/>
+      <c r="J3" s="74" t="n"/>
+      <c r="K3" s="74" t="n"/>
+      <c r="L3" s="74" t="n"/>
+      <c r="M3" s="74" t="n"/>
+      <c r="N3" s="77" t="n"/>
+      <c r="O3" s="77" t="n"/>
+      <c r="P3" s="74" t="n"/>
+    </row>
+    <row r="4" ht="54" customFormat="1" customHeight="1" s="81">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>BL_001</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>GPO-001</t>
+        </is>
       </c>
       <c r="C4" s="70">
-        <f t="shared" ref="C4:C9" si="0">ROW(A4)-3</f>
-        <v>1</v>
-      </c>
-      <c r="D4" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="79" t="s">
-        <v>83</v>
+        <f>ROW(A4)-3</f>
+        <v/>
+      </c>
+      <c r="D4" s="70" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="E4" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F4" s="70" t="inlineStr">
+        <is>
+          <t>Complete script GEN-002 to log into Ariba "Advanced" Buying and Invoicing.</t>
+        </is>
+      </c>
+      <c r="G4" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Login
+Password
+</t>
+        </is>
+      </c>
+      <c r="H4" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nexus Water Group homepage is presented. </t>
+        </is>
       </c>
       <c r="I4" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="70"/>
-    </row>
-    <row r="5" spans="1:16" s="81" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="70"/>
-      <c r="B5" s="70"/>
+      <c r="J4" s="70" t="n"/>
+      <c r="K4" s="70" t="n"/>
+      <c r="L4" s="70" t="n"/>
+      <c r="M4" s="70" t="n"/>
+      <c r="N4" s="70" t="n"/>
+      <c r="O4" s="70" t="n"/>
+      <c r="P4" s="70" t="n"/>
+    </row>
+    <row r="5" customFormat="1" s="81">
+      <c r="A5" s="70" t="n"/>
+      <c r="B5" s="70" t="n"/>
       <c r="C5" s="70">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D5" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="78"/>
-      <c r="H5" s="70" t="s">
-        <v>85</v>
+        <f>ROW(A5)-3</f>
+        <v/>
+      </c>
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="E5" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F5" s="89" t="inlineStr">
+        <is>
+          <t>Click on Catalog Tab</t>
+        </is>
+      </c>
+      <c r="G5" s="78" t="n"/>
+      <c r="H5" s="70" t="inlineStr">
+        <is>
+          <t>Catalog page is displayed</t>
+        </is>
       </c>
       <c r="I5" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-    </row>
-    <row r="6" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A6" s="70"/>
-      <c r="B6" s="70"/>
+      <c r="J5" s="70" t="n"/>
+      <c r="K5" s="70" t="n"/>
+      <c r="L5" s="70" t="n"/>
+      <c r="M5" s="70" t="n"/>
+      <c r="N5" s="70" t="n"/>
+      <c r="O5" s="70" t="n"/>
+      <c r="P5" s="70" t="n"/>
+    </row>
+    <row r="6" ht="36" customFormat="1" customHeight="1" s="81">
+      <c r="A6" s="70" t="n"/>
+      <c r="B6" s="70" t="n"/>
       <c r="C6" s="70">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="70" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="78" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="70"/>
+        <f>ROW(A6)-3</f>
+        <v/>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F6" s="70" t="inlineStr">
+        <is>
+          <t>On the search bar where it says "Search by part #, supplier name or keyword", type in the item you want to purchase.</t>
+        </is>
+      </c>
+      <c r="G6" s="78" t="inlineStr">
+        <is>
+          <t>Power Pen! Reading Comprehension Quiz Cards - Gr. 1</t>
+        </is>
+      </c>
+      <c r="H6" s="70" t="n"/>
       <c r="I6" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-    </row>
-    <row r="7" spans="1:16" s="81" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
+      <c r="J6" s="70" t="n"/>
+      <c r="K6" s="70" t="n"/>
+      <c r="L6" s="70" t="n"/>
+      <c r="M6" s="70" t="n"/>
+      <c r="N6" s="70" t="n"/>
+      <c r="O6" s="70" t="n"/>
+      <c r="P6" s="70" t="n"/>
+    </row>
+    <row r="7" ht="39.75" customFormat="1" customHeight="1" s="81">
+      <c r="A7" s="70" t="n"/>
+      <c r="B7" s="70" t="n"/>
       <c r="C7" s="70">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="70" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="78" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="70" t="s">
-        <v>45</v>
+        <f>ROW(A7)-3</f>
+        <v/>
+      </c>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="E7" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F7" s="70" t="inlineStr">
+        <is>
+          <t>From the search result, find the item. Enter the desired quantity  in the "Qty" box.</t>
+        </is>
+      </c>
+      <c r="G7" s="78" t="inlineStr">
+        <is>
+          <t>Quantity: 12</t>
+        </is>
+      </c>
+      <c r="H7" s="70" t="inlineStr">
+        <is>
+          <t>Desired quantity is indicated.</t>
+        </is>
       </c>
       <c r="I7" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-    </row>
-    <row r="8" spans="1:16" s="81" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
-      <c r="B8" s="70"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="70" t="n"/>
+      <c r="L7" s="70" t="n"/>
+      <c r="M7" s="70" t="n"/>
+      <c r="N7" s="70" t="n"/>
+      <c r="O7" s="70" t="n"/>
+      <c r="P7" s="70" t="n"/>
+    </row>
+    <row r="8" ht="36" customFormat="1" customHeight="1" s="81">
+      <c r="A8" s="70" t="n"/>
+      <c r="B8" s="70" t="n"/>
       <c r="C8" s="70">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D8" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="70" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70" t="s">
-        <v>47</v>
+        <f>ROW(A8)-3</f>
+        <v/>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="E8" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F8" s="70" t="inlineStr">
+        <is>
+          <t>Press "Add to Cart" button.</t>
+        </is>
+      </c>
+      <c r="G8" s="70" t="n"/>
+      <c r="H8" s="70" t="inlineStr">
+        <is>
+          <t>Shopping Cart popup  window appears.</t>
+        </is>
       </c>
       <c r="I8" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="70"/>
-    </row>
-    <row r="9" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
+      <c r="J8" s="70" t="n"/>
+      <c r="K8" s="70" t="n"/>
+      <c r="L8" s="70" t="n"/>
+      <c r="M8" s="70" t="n"/>
+      <c r="N8" s="70" t="n"/>
+      <c r="O8" s="70" t="n"/>
+      <c r="P8" s="70" t="n"/>
+    </row>
+    <row r="9" ht="54" customFormat="1" customHeight="1" s="81">
+      <c r="A9" s="70" t="n"/>
+      <c r="B9" s="70" t="n"/>
       <c r="C9" s="70">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D9" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="88" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="82" t="s">
-        <v>49</v>
+        <f>ROW(A9)-3</f>
+        <v/>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="E9" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F9" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen. Click on Proceed to Checkout button.
+</t>
+        </is>
+      </c>
+      <c r="G9" s="88" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="H9" s="82" t="inlineStr">
+        <is>
+          <t>Requisition screen appears. The system assigns the PR number to the document.</t>
+        </is>
       </c>
       <c r="I9" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-    </row>
-    <row r="10" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="70"/>
+      <c r="J9" s="70" t="n"/>
+      <c r="K9" s="70" t="n"/>
+      <c r="L9" s="70" t="n"/>
+      <c r="M9" s="70" t="n"/>
+      <c r="N9" s="70" t="n"/>
+      <c r="O9" s="70" t="n"/>
+      <c r="P9" s="70" t="n"/>
+    </row>
+    <row r="10" ht="36" customFormat="1" customHeight="1" s="81">
+      <c r="A10" s="70" t="n"/>
+      <c r="B10" s="70" t="n"/>
       <c r="C10" s="70">
-        <f t="shared" ref="C10:C17" si="1">ROW(A10)-3</f>
-        <v>7</v>
-      </c>
-      <c r="D10" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="83" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="78" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="70" t="s">
-        <v>52</v>
+        <f>ROW(A10)-3</f>
+        <v/>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Requisition Header</t>
+        </is>
+      </c>
+      <c r="E10" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F10" s="83" t="inlineStr">
+        <is>
+          <t>Enter the requistion title on "Requistion title" box.</t>
+        </is>
+      </c>
+      <c r="G10" s="78" t="inlineStr">
+        <is>
+          <t>AT-23</t>
+        </is>
+      </c>
+      <c r="H10" s="70" t="inlineStr">
+        <is>
+          <t>Requisition title is updated.</t>
+        </is>
       </c>
       <c r="I10" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="70"/>
-    </row>
-    <row r="11" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
-      <c r="B11" s="70"/>
+      <c r="J10" s="70" t="n"/>
+      <c r="K10" s="70" t="n"/>
+      <c r="L10" s="70" t="n"/>
+      <c r="M10" s="70" t="n"/>
+      <c r="N10" s="70" t="n"/>
+      <c r="O10" s="70" t="n"/>
+      <c r="P10" s="70" t="n"/>
+    </row>
+    <row r="11" ht="54" customFormat="1" customHeight="1" s="81">
+      <c r="A11" s="70" t="n"/>
+      <c r="B11" s="70" t="n"/>
       <c r="C11" s="70">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="90"/>
-      <c r="H11" s="70" t="s">
-        <v>54</v>
+        <f>ROW(A11)-3</f>
+        <v/>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Requisition Header</t>
+        </is>
+      </c>
+      <c r="E11" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F11" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enter or verify the remaing data elements on the Requistion screen.
+Note: Only "red " items should be editable.
+</t>
+        </is>
+      </c>
+      <c r="G11" s="90" t="n"/>
+      <c r="H11" s="70" t="inlineStr">
+        <is>
+          <t>Fields are updated without any error.</t>
+        </is>
       </c>
       <c r="I11" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-    </row>
-    <row r="12" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="70"/>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>Need-by is Today +5</t>
+        </is>
+      </c>
+      <c r="K11" s="70" t="n"/>
+      <c r="L11" s="70" t="n"/>
+      <c r="M11" s="70" t="n"/>
+      <c r="N11" s="70" t="n"/>
+      <c r="O11" s="70" t="n"/>
+      <c r="P11" s="70" t="n"/>
+    </row>
+    <row r="12" ht="54" customFormat="1" customHeight="1" s="81">
+      <c r="A12" s="70" t="n"/>
+      <c r="B12" s="70" t="n"/>
       <c r="C12" s="70">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="D12" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="91" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="92"/>
-      <c r="H12" s="90" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="80"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="70"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="70"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="70"/>
-    </row>
-    <row r="13" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
-      <c r="B13" s="70"/>
+        <f>ROW(A12)-3</f>
+        <v/>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Requisition Lines</t>
+        </is>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F12" s="91" t="inlineStr">
+        <is>
+          <t>Click on the checkbox in the line for the item (towards the item lines' top left).
+Click on Actions dropdown and then Edit Details.</t>
+        </is>
+      </c>
+      <c r="G12" s="92" t="n"/>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>Edit Detail page for the item is displayed.</t>
+        </is>
+      </c>
+      <c r="I12" s="80" t="n"/>
+      <c r="J12" s="70" t="n"/>
+      <c r="K12" s="70" t="n"/>
+      <c r="L12" s="70" t="n"/>
+      <c r="M12" s="70" t="n"/>
+      <c r="N12" s="70" t="n"/>
+      <c r="O12" s="70" t="n"/>
+      <c r="P12" s="70" t="n"/>
+    </row>
+    <row r="13" ht="54" customFormat="1" customHeight="1" s="81">
+      <c r="A13" s="70" t="n"/>
+      <c r="B13" s="70" t="n"/>
       <c r="C13" s="70">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="D13" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="91" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="92"/>
-      <c r="H13" s="90" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="80"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-    </row>
-    <row r="14" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
+        <f>ROW(A13)-3</f>
+        <v/>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Requisition Lines</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F13" s="91" t="inlineStr">
+        <is>
+          <t>Enter or verify the Line Item Details for the item.
+(Most details in this section is set to default)</t>
+        </is>
+      </c>
+      <c r="G13" s="92" t="inlineStr">
+        <is>
+          <t>No.: 1
+Full Description: Power Pen! Reading Comprehension Quiz Cards - Gr. 1
+Supplier Part Number: BD581
+Supplier Part Auxiliary ID: 
+Qty: 12
+UOM: each
+Price: $15.99 USD
+Price Unit Quantity: 1
+Unit Conversion: 
+Pricing Description: 
+Discount: 
+Net Amount: $191.88 USD Fx
+Charges: 
+Taxes: 
+Amount: $191.88 USD
+Commodity Code: Developmental and professional teaching aids and materials and accessories and supplies
+Supplier: LAKESHORE LEARNING MATERIALS
+Contact: LAKESHORE LEARNING MATERIALS [ select ]
+Service Item: No
+Contract: [ select ]</t>
+        </is>
+      </c>
+      <c r="H13" s="90" t="inlineStr">
+        <is>
+          <t>Fields are validated and updated if necessary.</t>
+        </is>
+      </c>
+      <c r="I13" s="80" t="n"/>
+      <c r="J13" s="70" t="n"/>
+      <c r="K13" s="70" t="n"/>
+      <c r="L13" s="70" t="n"/>
+      <c r="M13" s="70" t="n"/>
+      <c r="N13" s="70" t="n"/>
+      <c r="O13" s="70" t="n"/>
+      <c r="P13" s="70" t="n"/>
+    </row>
+    <row r="14" ht="36" customFormat="1" customHeight="1" s="81">
+      <c r="A14" s="70" t="n"/>
+      <c r="B14" s="70" t="n"/>
       <c r="C14" s="70">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="D14" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="93" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="91"/>
-      <c r="H14" s="70" t="s">
-        <v>57</v>
+        <f>ROW(A14)-3</f>
+        <v/>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>Requisition Lines</t>
+        </is>
+      </c>
+      <c r="E14" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F14" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scroll down to Accounting - by Line Item Section
+Enter or  verify the information in the Accounting  section. </t>
+        </is>
+      </c>
+      <c r="G14" s="91" t="inlineStr">
+        <is>
+          <t>Account Type: Expense
+Bill To: Ariba - Pittsburgh
+Cost Center: Ariba - Office of the CEO
+Business Unit: Ariba - Marketing
+Company: Ariba - Company 1
+Account: ARIBA - Expense Account 1
+Project: (no value)</t>
+        </is>
+      </c>
+      <c r="H14" s="70" t="inlineStr">
+        <is>
+          <t>Fields are updated</t>
+        </is>
       </c>
       <c r="I14" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="70"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-    </row>
-    <row r="15" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A15" s="70"/>
-      <c r="B15" s="70"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
+    </row>
+    <row r="15" ht="36" customFormat="1" customHeight="1" s="81">
+      <c r="A15" s="70" t="n"/>
+      <c r="B15" s="70" t="n"/>
       <c r="C15" s="70">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="D15" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="90"/>
-      <c r="H15" s="70" t="s">
-        <v>57</v>
+        <f>ROW(A15)-3</f>
+        <v/>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Requisition Lines</t>
+        </is>
+      </c>
+      <c r="E15" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F15" s="90" t="inlineStr">
+        <is>
+          <t>Enter or  verify the information in the Shipping - by Line Item section.</t>
+        </is>
+      </c>
+      <c r="G15" s="90" t="inlineStr">
+        <is>
+          <t>Ship_To: Ariba - Pittsburgh
+Deliver_To: Samit Paudel
+Need-by_Date: Tue, 29 Apr, 2025</t>
+        </is>
+      </c>
+      <c r="H15" s="70" t="inlineStr">
+        <is>
+          <t>Fields are updated</t>
+        </is>
       </c>
       <c r="I15" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-    </row>
-    <row r="16" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.35">
-      <c r="A16" s="70"/>
-      <c r="B16" s="70"/>
+      <c r="J15" s="70" t="n"/>
+      <c r="K15" s="70" t="n"/>
+      <c r="L15" s="70" t="n"/>
+      <c r="M15" s="70" t="n"/>
+      <c r="N15" s="70" t="n"/>
+      <c r="O15" s="70" t="n"/>
+      <c r="P15" s="70" t="n"/>
+    </row>
+    <row r="16" ht="36" customFormat="1" customHeight="1" s="81">
+      <c r="A16" s="70" t="n"/>
+      <c r="B16" s="70" t="n"/>
       <c r="C16" s="70">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="D16" s="70" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="84" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85" t="s">
-        <v>60</v>
+        <f>ROW(A16)-3</f>
+        <v/>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Requisition</t>
+        </is>
+      </c>
+      <c r="E16" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F16" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Press "Submit"  to submit the requisition for approval. </t>
+        </is>
+      </c>
+      <c r="G16" s="85" t="n"/>
+      <c r="H16" s="85" t="inlineStr">
+        <is>
+          <t>Message appears "Your requisition has been sent for approval.</t>
+        </is>
       </c>
       <c r="I16" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-    </row>
-    <row r="17" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.4">
-      <c r="A17" s="70"/>
-      <c r="B17" s="70"/>
+      <c r="J16" s="70" t="n"/>
+      <c r="K16" s="70" t="n"/>
+      <c r="L16" s="70" t="n"/>
+      <c r="M16" s="70" t="n"/>
+      <c r="N16" s="70" t="n"/>
+      <c r="O16" s="70" t="n"/>
+      <c r="P16" s="70" t="n"/>
+    </row>
+    <row r="17" ht="54" customFormat="1" customHeight="1" s="81">
+      <c r="A17" s="70" t="n"/>
+      <c r="B17" s="70" t="n"/>
       <c r="C17" s="70">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="84" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="85" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="82" t="s">
-        <v>64</v>
+        <f>ROW(A17)-3</f>
+        <v/>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>View Approval Flow</t>
+        </is>
+      </c>
+      <c r="E17" s="70" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="F17" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Click on View Requisition to display the created requisiton. </t>
+        </is>
+      </c>
+      <c r="G17" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Submitted</t>
+        </is>
+      </c>
+      <c r="H17" s="82" t="inlineStr">
+        <is>
+          <t>The PR is now on Submitted status.
+Approval Flow is now active shown by green flow.</t>
+        </is>
       </c>
       <c r="I17" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
+      <c r="J17" s="70" t="n"/>
+      <c r="K17" s="70" t="n"/>
+      <c r="L17" s="70" t="n"/>
+      <c r="M17" s="70" t="n"/>
+      <c r="N17" s="70" t="n"/>
+      <c r="O17" s="70" t="n"/>
+      <c r="P17" s="70" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="P1:P2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="C1:C2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="M1:M2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="O1:O2"/>
     <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4:N17">
+    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"10 - Not Started,20 - In-Process,30 - TPR Hold,40 - DEV Hold,50 - Pass,60 - N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K17">
+    <dataValidation sqref="K4:K17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E17">
+    <dataValidation sqref="E4:E17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"AP,Buyer,PO Approv,Inv Approv,Watcher,SAP Tech Team,Prem Tech,Prem Funct"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="61" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="landscape" scale="61" fitToHeight="10" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:R46"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:R46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="2" customWidth="1"/>
-    <col min="3" max="7" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8" max="9" width="14.33203125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="11.6640625" style="1" customWidth="1"/>
-    <col min="12" max="17" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col width="14.88671875" customWidth="1" style="2" min="1" max="1"/>
+    <col width="8.44140625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="14.33203125" customWidth="1" style="2" min="3" max="7"/>
+    <col width="14.33203125" customWidth="1" style="1" min="8" max="9"/>
+    <col width="11.6640625" customWidth="1" style="1" min="10" max="11"/>
+    <col width="14.33203125" bestFit="1" customWidth="1" style="1" min="12" max="17"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="1" min="18" max="18"/>
+    <col width="9.109375" customWidth="1" style="1" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="R3"/>
-    </row>
-    <row r="4" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-      <c r="R4"/>
-    </row>
-    <row r="5" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4">
+    <row r="2" ht="17.25" customHeight="1" thickBot="1"/>
+    <row r="3" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Count of Status</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="21" t="n"/>
+    </row>
+    <row r="4" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Scenario Number</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>10 - Not Started</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>20 - In-Process</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>30 - TPR Hold</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>40 - DEV Hold</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>50 - Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr">
+        <is>
+          <t>60 - N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="13.2" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>PP_018</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>RTR</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="6">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-      <c r="R5"/>
-    </row>
-    <row r="6" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="27">
+    </row>
+    <row r="6" ht="13.2" customHeight="1">
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>PTP</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27">
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
+      <c r="H6" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-      <c r="R6"/>
-    </row>
-    <row r="7" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27">
+    </row>
+    <row r="7" ht="13.2" customHeight="1">
+      <c r="A7" s="26" t="n"/>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28">
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7"/>
-      <c r="R7"/>
-    </row>
-    <row r="8" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27">
+    </row>
+    <row r="8" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>IMWM</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
+      <c r="H8" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-      <c r="P8"/>
-      <c r="Q8"/>
-      <c r="R8"/>
-    </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10">
+    </row>
+    <row r="9" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>PP_018 Total</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10">
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9"/>
-      <c r="R9"/>
-    </row>
-    <row r="10" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10">
+    </row>
+    <row r="10" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>ZZZ999</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-    </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4">
+    </row>
+    <row r="11" ht="17.25" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>ZZZ999 Total</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-    </row>
-    <row r="12" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10">
+    </row>
+    <row r="12" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13"/>
-      <c r="R13"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-      <c r="R14"/>
-    </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-      <c r="R15"/>
-    </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16"/>
-      <c r="R16"/>
-    </row>
-    <row r="17" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17"/>
-    </row>
-    <row r="18" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18"/>
-    </row>
-    <row r="19" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19"/>
-      <c r="P19"/>
-      <c r="Q19"/>
-      <c r="R19"/>
-    </row>
-    <row r="20" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-      <c r="R20"/>
-    </row>
-    <row r="21" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-      <c r="R21"/>
-    </row>
-    <row r="22" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
-      <c r="P22"/>
-      <c r="Q22"/>
-      <c r="R22"/>
-    </row>
-    <row r="23" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-      <c r="R23"/>
-    </row>
-    <row r="24" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24"/>
-      <c r="P24"/>
-      <c r="Q24"/>
-      <c r="R24"/>
-    </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
-      <c r="R25"/>
-    </row>
-    <row r="26" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26"/>
-    </row>
-    <row r="27" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-      <c r="R27"/>
-    </row>
-    <row r="28" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-    </row>
-    <row r="29" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29"/>
-      <c r="R29"/>
-    </row>
-    <row r="30" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-    </row>
-    <row r="31" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31"/>
-      <c r="R31"/>
-    </row>
-    <row r="32" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-    </row>
-    <row r="33" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-    </row>
-    <row r="34" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-    </row>
-    <row r="35" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-    </row>
-    <row r="36" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36"/>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-      <c r="P36"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-    </row>
-    <row r="37" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
-      <c r="N37"/>
-      <c r="O37"/>
-      <c r="P37"/>
-      <c r="Q37"/>
-      <c r="R37"/>
-    </row>
-    <row r="38" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-      <c r="K38"/>
-      <c r="L38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
-      <c r="P38"/>
-      <c r="Q38"/>
-      <c r="R38"/>
-    </row>
-    <row r="39" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="L39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
-      <c r="P39"/>
-      <c r="Q39"/>
-      <c r="R39"/>
-    </row>
-    <row r="40" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40"/>
-      <c r="C40"/>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-      <c r="Q40"/>
-      <c r="R40"/>
-    </row>
-    <row r="41" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="L41"/>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41"/>
-      <c r="P41"/>
-      <c r="Q41"/>
-      <c r="R41"/>
-    </row>
-    <row r="42" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
-      <c r="Q42"/>
-      <c r="R42"/>
-    </row>
-    <row r="43" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
-      <c r="P43"/>
-      <c r="Q43"/>
-      <c r="R43"/>
-    </row>
-    <row r="44" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44"/>
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="O44"/>
-      <c r="P44"/>
-      <c r="Q44"/>
-      <c r="R44"/>
-    </row>
-    <row r="45" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
-      <c r="R45"/>
-    </row>
-    <row r="46" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
-      <c r="P46"/>
-      <c r="Q46"/>
-      <c r="R46"/>
-    </row>
+    </row>
+    <row r="13" ht="17.25" customHeight="1"/>
+    <row r="14" ht="17.25" customHeight="1"/>
+    <row r="15" ht="17.25" customHeight="1"/>
+    <row r="16" ht="17.25" customHeight="1"/>
+    <row r="17" ht="17.25" customHeight="1"/>
+    <row r="18" ht="17.25" customHeight="1"/>
+    <row r="19" ht="17.25" customHeight="1"/>
+    <row r="20" ht="17.25" customHeight="1"/>
+    <row r="21" ht="17.25" customHeight="1"/>
+    <row r="22" ht="17.25" customHeight="1"/>
+    <row r="23" ht="17.25" customHeight="1"/>
+    <row r="24" ht="17.25" customHeight="1"/>
+    <row r="25" ht="17.25" customHeight="1"/>
+    <row r="26" ht="17.25" customHeight="1"/>
+    <row r="27" ht="17.25" customHeight="1"/>
+    <row r="28" ht="17.25" customHeight="1"/>
+    <row r="29" ht="17.25" customHeight="1"/>
+    <row r="30" ht="17.25" customHeight="1"/>
+    <row r="31" ht="17.25" customHeight="1"/>
+    <row r="32" ht="17.25" customHeight="1"/>
+    <row r="33" ht="17.25" customHeight="1"/>
+    <row r="34" ht="17.25" customHeight="1"/>
+    <row r="35" ht="17.25" customHeight="1"/>
+    <row r="36" ht="17.25" customHeight="1"/>
+    <row r="37" ht="17.25" customHeight="1"/>
+    <row r="38" ht="17.25" customHeight="1"/>
+    <row r="39" ht="17.25" customHeight="1"/>
+    <row r="40" ht="17.25" customHeight="1"/>
+    <row r="41" ht="17.25" customHeight="1"/>
+    <row r="42" ht="17.25" customHeight="1"/>
+    <row r="43" ht="17.25" customHeight="1"/>
+    <row r="44" ht="17.25" customHeight="1"/>
+    <row r="45" ht="17.25" customHeight="1"/>
+    <row r="46" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010019714232D8671D41B688C3A48C5AE621" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d53d216ca0852b3df112c80684e44a04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0590885-0391-4acc-a1a2-62bdd649afdc" xmlns:ns3="f203ef26-be28-437c-ae01-5f41441de6d3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a994f462a7971573747b1ee30b6f4c90" ns2:_="" ns3:_="">
-    <xsd:import namespace="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
-    <xsd:import namespace="f203ef26-be28-437c-ae01-5f41441de6d3"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0590885-0391-4acc-a1a2-62bdd649afdc" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2cfdae59-7532-4cc8-8ce8-63e07576e745" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f203ef26-be28-437c-ae01-5f41441de6d3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{af0a4373-ad75-4169-a61b-b6de68ac2aea}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f203ef26-be28-437c-ae01-5f41441de6d3">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="f203ef26-be28-437c-ae01-5f41441de6d3">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="f203ef26-be28-437c-ae01-5f41441de6d3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0590885-0391-4acc-a1a2-62bdd649afdc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C2D16A-6A14-4FCF-9B7F-81D5BCF9F508}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B1B1D8-E7B0-43D3-BF30-A53ECE29C72F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
-    <ds:schemaRef ds:uri="f203ef26-be28-437c-ae01-5f41441de6d3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56BCB5A8-855F-4A49-B3E4-B6B1DAD57931}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E58E092-0497-4CF3-8876-CC340FCDDFD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f203ef26-be28-437c-ae01-5f41441de6d3"/>
-    <ds:schemaRef ds:uri="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/excel_test_cases_updated/test_create_pr_copy.xlsx
+++ b/excel_test_cases_updated/test_create_pr_copy.xlsx
@@ -1,180 +1,881 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samit paudel\Downloads\ariba_automation\sap_test_automation\excel_test_cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="878" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="878" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario Cover Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Steps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="References" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Scenario Metrics " sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Scenario Cover Sheet" sheetId="15" r:id="rId1"/>
+    <sheet name="Steps" sheetId="17" r:id="rId2"/>
+    <sheet name="References" sheetId="18" r:id="rId3"/>
+    <sheet name="Scenario Metrics " sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Steps!$A$1:$Q$14</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
+  <si>
+    <t xml:space="preserve">Scenario Owner: </t>
+  </si>
+  <si>
+    <t>Test Cycle:</t>
+  </si>
+  <si>
+    <t>Scenario ID:</t>
+  </si>
+  <si>
+    <t>GPO-001</t>
+  </si>
+  <si>
+    <t>Test Objective:</t>
+  </si>
+  <si>
+    <t>Create PR and PO in guided buying.</t>
+  </si>
+  <si>
+    <t>Scenario Description:</t>
+  </si>
+  <si>
+    <t>Long Description Scenario Summary for items to be tested</t>
+  </si>
+  <si>
+    <t>Search catalog for items
+Add items to cart
+Complete requisition details and submit
+Review PR approval flow 
+Confirm PO generation
+Create associated receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Data Requirements</t>
+  </si>
+  <si>
+    <t>Legacy Reference</t>
+  </si>
+  <si>
+    <t>SAP Reference</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prerequisite </t>
+  </si>
+  <si>
+    <t>Key RICEF Objects</t>
+  </si>
+  <si>
+    <t>Master Data Validation</t>
+  </si>
+  <si>
+    <t>SAP PO Post and Validation</t>
+  </si>
+  <si>
+    <t>SAP Invoice to SAP</t>
+  </si>
+  <si>
+    <t>Payment Remitance Validation to Ariba</t>
+  </si>
+  <si>
+    <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Scenario Number</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description </t>
+  </si>
+  <si>
+    <t>Test Data / Test Execution</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Step Completed
+Sucessfullyåç</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>FI Impact</t>
+  </si>
+  <si>
+    <t>RICEF Tested</t>
+  </si>
+  <si>
+    <t>TPR #</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Tester/User ID</t>
+  </si>
+  <si>
+    <t>Y or N</t>
+  </si>
+  <si>
+    <t>Scenario No.</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>BL_001</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Buyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login
+Password
+</t>
+  </si>
+  <si>
+    <t>Catalog</t>
+  </si>
+  <si>
+    <t>Desired quantity is indicated.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Press</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add to Cart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" button.</t>
+    </r>
+  </si>
+  <si>
+    <t>Shopping Cart popup  window appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>Requisition screen appears. The system assigns the PR number to the document.</t>
+  </si>
+  <si>
+    <t>Requisition Header</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enter the requistion title on "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Requistion title</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" box.</t>
+    </r>
+  </si>
+  <si>
+    <t>Requisition title is updated.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enter or verify the remaing data elements on the Requistion screen.
+Note: Only "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">red </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" items should be editable.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Fields are updated without any error.</t>
+  </si>
+  <si>
+    <t>Need-by is Today +5</t>
+  </si>
+  <si>
+    <t>Requisition Lines</t>
+  </si>
+  <si>
+    <t>Fields are updated</t>
+  </si>
+  <si>
+    <t>Requisition</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Press "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"  to submit the requisition for approval. </t>
+    </r>
+  </si>
+  <si>
+    <t>Message appears "Your requisition has been sent for approval.</t>
+  </si>
+  <si>
+    <t>View Approval Flow</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Click on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Requisition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to display the created requisiton. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Submitted</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The PR is now on Submitted status.
+Approval Flow is now active shown by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>green flow.</t>
+    </r>
+  </si>
+  <si>
+    <t>Count of Status</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>10 - Not Started</t>
+  </si>
+  <si>
+    <t>20 - In-Process</t>
+  </si>
+  <si>
+    <t>30 - TPR Hold</t>
+  </si>
+  <si>
+    <t>40 - DEV Hold</t>
+  </si>
+  <si>
+    <t>50 - Pass</t>
+  </si>
+  <si>
+    <t>60 - N/A</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>PP_018</t>
+  </si>
+  <si>
+    <t>RTR</t>
+  </si>
+  <si>
+    <t>PTP</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>IMWM</t>
+  </si>
+  <si>
+    <t>PP_018 Total</t>
+  </si>
+  <si>
+    <t>ZZZ999</t>
+  </si>
+  <si>
+    <t>ZZZ999 Total</t>
+  </si>
+  <si>
+    <t>Complete script GEN-002 to log into Ariba "Advanced" Buying and Invoicing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexus Water Group homepage is presented. </t>
+  </si>
+  <si>
+    <t>Click on Catalog Tab</t>
+  </si>
+  <si>
+    <t>Catalog page is displayed</t>
+  </si>
+  <si>
+    <t>On the search bar where it says "Search by part #, supplier name or keyword", type in the item you want to purchase.</t>
+  </si>
+  <si>
+    <t>Book Bins - Set of 12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From the search result, find the item. Enter the desired quantity  in the "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> box.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen. Click on Proceed to Checkout button.
+</t>
+  </si>
+  <si>
+    <t>AT-1</t>
+  </si>
+  <si>
+    <r>
+      <t>Click on the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkbox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the line for the item (towards the item lines' top left).
+Click on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dropdown and then </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Edit Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Edit Detail page for the item is displayed.</t>
+  </si>
+  <si>
+    <r>
+      <t>Scroll down to Accounting - by Line Item Section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter or  verify the information in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accounting  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">section. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Enter or  verify the information in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Shipping - by Line Item </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>section.</t>
+    </r>
+  </si>
+  <si>
+    <t>Enter or verify the Line Item Details for the item.
+(Most details in this section is set to default)</t>
+  </si>
+  <si>
+    <t>Fields are validated and updated if necessary.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="8"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="12"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <i val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
-      <color rgb="FF00B050"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF262626"/>
       <name val="Calibri"/>
-      <color rgb="FF262626"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF00B050"/>
-      <sz val="16"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -216,7 +917,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -796,413 +1497,316 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="123">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="1" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="1" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1392,58 +1996,58 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
@@ -1496,22 +2100,56 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00B0F0"/>
+      <color rgb="FFE2EFDA"/>
+      <color rgb="FFCEE4CB"/>
+      <color rgb="FFFDE9D9"/>
+      <color rgb="FFE4DFEC"/>
+      <color rgb="FFDDEBF7"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" refreshedBy="Browning G Hollomon" refreshedDate="39386.43617974537" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1" r:id="rId1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Browning G Hollomon" refreshedDate="39386.436179745368" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final"/>
+    <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final" r:id="rId2"/>
   </cacheSource>
   <cacheFields count="15">
-    <cacheField name="Scenario Number" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="28" containsBlank="1">
+    <cacheField name="Scenario Number" numFmtId="0">
+      <sharedItems containsBlank="1" count="28">
         <m/>
         <s v="Demand Planning"/>
         <s v="FTS001"/>
@@ -1542,11 +2180,11 @@
         <s v="OTC001" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Step" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsInteger="1" containsNumber="1" containsString="0" minValue="1" maxValue="46"/>
+    <cacheField name="Step" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="46"/>
     </cacheField>
-    <cacheField name="Team" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="7" containsBlank="1">
+    <cacheField name="Team" numFmtId="0">
+      <sharedItems containsBlank="1" count="7">
         <m/>
         <s v="FTS"/>
         <s v="PTP"/>
@@ -1556,35 +2194,35 @@
         <s v="XXX" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Description " uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Description " numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tcode" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Tcode" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tester" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Tester" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Test Data / Test Execution" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Test Data / Test Execution" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Expected Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Expected Result" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Actual Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Actual Result" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="FI Impact" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="FI Impact" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="RICEF Tested" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="RICEF Tested" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="TPR #" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="TPR #" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Status" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="34" containsBlank="1">
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems containsBlank="1" count="34">
         <m/>
         <s v="50 - Pass"/>
         <s v="60 - N/A"/>
@@ -1621,18 +2259,23 @@
         <s v="20 In Process" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="User ID" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="User ID" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Comments" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="Comments" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="137">
   <r>
     <x v="0"/>
     <m/>
@@ -3966,231 +4609,231 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" dataCaption="Data" showError="0" showMissing="1" updatedVersion="3" minRefreshableVersion="0" asteriskTotals="0" showItems="1" editData="0" disableFieldList="0" showCalcMbrs="1" visualTotals="1" showMultipleLabel="1" showDataDropDown="1" showDrill="1" printDrill="0" showMemberPropertyTips="0" showDataTips="1" enableWizard="1" enableDrill="1" enableFieldProperties="1" preserveFormatting="1" useAutoFormatting="1" pageWrap="0" pageOverThenDown="0" subtotalHiddenItems="0" rowGrandTotals="1" colGrandTotals="1" fieldPrintTitles="0" itemPrintTitles="1" mergeItem="0" showDropZones="1" createdVersion="1" indent="0" showEmptyRow="0" showEmptyCol="0" showHeaders="1" compact="0" outline="0" outlineData="0" compactData="0" published="0" gridDropZones="1" immersive="1" multipleFieldFilters="0" chartFormat="0" fieldListSortAscending="0" mdxSubqueries="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" r:id="rId1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:J12" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="15">
-    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="29">
-        <item t="data" h="1" sd="1" m="1" x="27"/>
-        <item t="data" h="1" sd="1" x="0"/>
-        <item t="data" h="1" sd="1" m="1" x="10"/>
-        <item n="PP_018" t="data" sd="1" x="2"/>
-        <item t="data" sd="1" m="1" x="8"/>
-        <item t="data" sd="1" x="7"/>
-        <item t="data" sd="1" m="1" x="16"/>
-        <item t="data" sd="1" m="1" x="18"/>
-        <item t="data" sd="1" m="1" x="20"/>
-        <item t="data" sd="1" m="1" x="22"/>
-        <item t="data" sd="1" m="1" x="23"/>
-        <item t="data" sd="1" m="1" x="24"/>
-        <item t="data" sd="1" m="1" x="25"/>
-        <item t="data" sd="1" m="1" x="26"/>
-        <item t="data" sd="1" m="1" x="9"/>
-        <item t="data" sd="1" m="1" x="11"/>
-        <item t="data" sd="1" m="1" x="12"/>
-        <item t="data" sd="1" m="1" x="13"/>
-        <item t="data" sd="1" m="1" x="14"/>
-        <item t="data" sd="1" m="1" x="15"/>
-        <item t="data" sd="1" m="1" x="17"/>
-        <item t="data" sd="1" m="1" x="19"/>
-        <item t="data" sd="1" m="1" x="21"/>
-        <item t="data" sd="1" x="1"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="5"/>
-        <item t="data" sd="1" x="6"/>
-        <item t="default" sd="1"/>
+        <item h="1" m="1" x="27"/>
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="10"/>
+        <item n="PP_018" x="2"/>
+        <item m="1" x="8"/>
+        <item x="7"/>
+        <item m="1" x="16"/>
+        <item m="1" x="18"/>
+        <item m="1" x="20"/>
+        <item m="1" x="22"/>
+        <item m="1" x="23"/>
+        <item m="1" x="24"/>
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="9"/>
+        <item m="1" x="11"/>
+        <item m="1" x="12"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
+        <item m="1" x="17"/>
+        <item m="1" x="19"/>
+        <item m="1" x="21"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="8">
-        <item t="data" h="1" sd="1" x="0"/>
-        <item t="data" sd="1" m="1" x="5"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="2"/>
-        <item n="PP" t="data" sd="1" x="1"/>
-        <item t="data" sd="1" m="1" x="6"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="default" sd="1"/>
+        <item h="1" x="0"/>
+        <item m="1" x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item n="PP" x="1"/>
+        <item m="1" x="6"/>
+        <item x="3"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField axis="axisCol" dataField="1" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisCol" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="35">
-        <item t="data" sd="1" m="1" x="12"/>
-        <item t="data" sd="1" m="1" x="16"/>
-        <item t="data" sd="1" m="1" x="29"/>
-        <item t="data" sd="1" m="1" x="31"/>
-        <item t="data" sd="1" m="1" x="24"/>
-        <item t="data" sd="1" x="0"/>
-        <item t="data" sd="1" m="1" x="17"/>
-        <item t="data" sd="1" m="1" x="33"/>
-        <item t="data" sd="1" m="1" x="26"/>
-        <item t="data" sd="1" m="1" x="13"/>
-        <item t="data" sd="1" m="1" x="9"/>
-        <item t="data" sd="1" m="1" x="25"/>
-        <item t="data" sd="1" m="1" x="8"/>
-        <item t="data" sd="1" m="1" x="28"/>
-        <item t="data" sd="1" m="1" x="19"/>
-        <item t="data" sd="1" m="1" x="30"/>
-        <item t="data" sd="1" m="1" x="15"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="5"/>
-        <item t="data" sd="1" x="6"/>
-        <item t="data" sd="1" m="1" x="10"/>
-        <item t="data" sd="1" m="1" x="18"/>
-        <item t="data" sd="1" m="1" x="11"/>
-        <item t="data" sd="1" m="1" x="22"/>
-        <item t="data" sd="1" m="1" x="32"/>
-        <item t="data" sd="1" m="1" x="20"/>
-        <item t="data" sd="1" m="1" x="27"/>
-        <item t="data" sd="1" m="1" x="14"/>
-        <item t="data" sd="1" m="1" x="23"/>
-        <item t="data" sd="1" m="1" x="7"/>
-        <item t="data" sd="1" m="1" x="21"/>
-        <item t="data" sd="1" x="1"/>
-        <item t="data" sd="1" x="2"/>
-        <item t="default" sd="1"/>
+        <item m="1" x="12"/>
+        <item m="1" x="16"/>
+        <item m="1" x="29"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="0"/>
+        <item m="1" x="17"/>
+        <item m="1" x="33"/>
+        <item m="1" x="26"/>
+        <item m="1" x="13"/>
+        <item m="1" x="9"/>
+        <item m="1" x="25"/>
+        <item m="1" x="8"/>
+        <item m="1" x="28"/>
+        <item m="1" x="19"/>
+        <item m="1" x="30"/>
+        <item m="1" x="15"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item m="1" x="10"/>
+        <item m="1" x="18"/>
+        <item m="1" x="11"/>
+        <item m="1" x="22"/>
+        <item m="1" x="32"/>
+        <item m="1" x="20"/>
+        <item m="1" x="27"/>
+        <item m="1" x="14"/>
+        <item m="1" x="23"/>
+        <item m="1" x="7"/>
+        <item m="1" x="21"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
     <field x="2"/>
   </rowFields>
   <rowItems count="8">
-    <i t="data" r="0" i="0">
+    <i>
       <x v="3"/>
       <x v="2"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="3"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="4"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="6"/>
     </i>
-    <i t="default" r="0" i="0">
+    <i t="default">
       <x v="3"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="5"/>
       <x v="4"/>
     </i>
-    <i t="default" r="0" i="0">
+    <i t="default">
       <x v="5"/>
     </i>
-    <i t="grand" r="0" i="0">
-      <x v="0"/>
+    <i t="grand">
+      <x/>
     </i>
   </rowItems>
   <colFields count="1">
     <field x="12"/>
   </colFields>
   <colItems count="8">
-    <i t="data" r="0" i="0">
+    <i>
       <x v="5"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="17"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="18"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="19"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="20"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="32"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="33"/>
     </i>
-    <i t="grand" r="0" i="0">
-      <x v="0"/>
+    <i t="grand">
+      <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Status" fld="12" subtotal="count" showDataAs="normal" baseField="0" baseItem="0"/>
+    <dataField name="Count of Status" fld="12" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="44">
-    <format action="formatting" dxfId="43">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
+    <format dxfId="43">
+      <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="42">
+    <format dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="41">
+    <format dxfId="41">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="40">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="39">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="38">
+    <format dxfId="38">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="37">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="36">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="35">
+    <format dxfId="35">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="34">
+    <format dxfId="34">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="33">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="32">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="31">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="30">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="29">
+    <format dxfId="29">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="28">
+    <format dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="27">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12">
+          <reference field="12" count="5">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4200,10 +4843,10 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="26">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="26">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" selected="0">
+          <reference field="12" count="5" selected="0">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4213,16 +4856,16 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="25">
+    <format dxfId="25">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="24">
+    <format dxfId="24">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="23">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12">
+          <reference field="12" count="5">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4232,176 +4875,181 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="22">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0">
+          <reference field="0" count="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="21">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="20">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="19">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0">
+          <reference field="0" count="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="18">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="17">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="2"/>
           </reference>
-          <reference field="2">
+          <reference field="2" count="1">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="16">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="15">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="15">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0" defaultSubtotal="1">
+          <reference field="0" count="1" selected="0" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="14">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="13">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="13">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0" defaultSubtotal="1">
+          <reference field="0" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="12">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="12">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="5"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="11">
+    <format dxfId="11">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="10">
+    <format dxfId="10">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="9">
+    <format dxfId="9">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="8">
+    <format dxfId="8">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="7">
+    <format dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="6">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0"/>
+          <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="5">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="4">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="3"/>
           </reference>
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="3">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="5"/>
           </reference>
-          <reference field="2">
+          <reference field="2" count="2">
             <x v="4"/>
             <x v="6"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="2">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="1">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12"/>
+          <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="0">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12"/>
+          <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
@@ -4691,1706 +5339,2482 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="25.88671875" customWidth="1" style="38" min="1" max="2"/>
-    <col width="25" customWidth="1" style="38" min="3" max="3"/>
-    <col width="25.88671875" customWidth="1" style="38" min="4" max="4"/>
-    <col width="34.88671875" customWidth="1" style="38" min="5" max="5"/>
-    <col width="40.88671875" customWidth="1" style="38" min="6" max="14"/>
-    <col width="9.109375" customWidth="1" style="38" min="15" max="16384"/>
+    <col min="1" max="2" width="25.88671875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="25" style="38" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" style="38" customWidth="1"/>
+    <col min="6" max="14" width="40.88671875" style="38" customWidth="1"/>
+    <col min="15" max="16384" width="9.109375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scenario Owner: </t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="36" t="n"/>
-      <c r="E1" s="37" t="n"/>
-    </row>
-    <row r="2" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Test Cycle:</t>
-        </is>
-      </c>
-      <c r="B2" s="96" t="n"/>
-      <c r="C2" s="123" t="n"/>
-      <c r="D2" s="97" t="n"/>
-      <c r="E2" s="41" t="n"/>
-    </row>
-    <row r="3" ht="12" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>Scenario ID:</t>
-        </is>
-      </c>
-      <c r="B3" s="124" t="inlineStr">
-        <is>
-          <t>GPO-001</t>
-        </is>
-      </c>
-      <c r="C3" s="125" t="n"/>
-      <c r="D3" s="125" t="n"/>
-      <c r="E3" s="126" t="n"/>
-    </row>
-    <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>Test Objective:</t>
-        </is>
-      </c>
-      <c r="B4" s="124" t="inlineStr">
-        <is>
-          <t>Create PR and PO in guided buying.</t>
-        </is>
-      </c>
-      <c r="C4" s="125" t="n"/>
-      <c r="D4" s="125" t="n"/>
-      <c r="E4" s="126" t="n"/>
-    </row>
-    <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="127" t="inlineStr">
-        <is>
-          <t>Scenario Description:</t>
-        </is>
-      </c>
-      <c r="B5" s="105" t="n"/>
-      <c r="E5" s="128" t="n"/>
-    </row>
-    <row r="6" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A6" s="129" t="n"/>
-      <c r="B6" s="130" t="n"/>
-      <c r="C6" s="130" t="n"/>
-      <c r="D6" s="130" t="n"/>
-      <c r="E6" s="131" t="n"/>
-    </row>
-    <row r="7" ht="12" customHeight="1" thickBot="1">
-      <c r="A7" s="42" t="n"/>
-      <c r="E7" s="43" t="n"/>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="127" t="inlineStr">
-        <is>
-          <t>Long Description Scenario Summary for items to be tested</t>
-        </is>
-      </c>
-      <c r="B8" s="132" t="n"/>
-      <c r="C8" s="132" t="n"/>
-      <c r="D8" s="132" t="n"/>
-      <c r="E8" s="133" t="n"/>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="134" t="inlineStr">
-        <is>
-          <t>Search catalog for items
-Add items to cart
-Complete requisition details and submit
-Review PR approval flow 
-Confirm PO generation
-Create associated receipt</t>
-        </is>
-      </c>
-      <c r="B9" s="135" t="n"/>
-      <c r="C9" s="135" t="n"/>
-      <c r="D9" s="135" t="n"/>
-      <c r="E9" s="136" t="n"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="137" t="n"/>
-      <c r="E10" s="128" t="n"/>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="137" t="n"/>
-      <c r="E11" s="128" t="n"/>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="137" t="n"/>
-      <c r="E12" s="128" t="n"/>
-      <c r="F12" s="38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="137" t="n"/>
-      <c r="E13" s="128" t="n"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="137" t="n"/>
-      <c r="E14" s="128" t="n"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A15" s="137" t="n"/>
-      <c r="E15" s="128" t="n"/>
-    </row>
-    <row r="16" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>Data Requirements</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>Legacy Reference</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>SAP Reference</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="E16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="69" t="n"/>
-      <c r="B17" s="113" t="n"/>
-      <c r="C17" s="95" t="n"/>
-      <c r="D17" s="138" t="n"/>
-      <c r="E17" s="136" t="n"/>
-    </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="A18" s="67" t="n"/>
-      <c r="B18" s="95" t="n"/>
-      <c r="C18" s="95" t="n"/>
-      <c r="D18" s="137" t="n"/>
-      <c r="E18" s="128" t="n"/>
-    </row>
-    <row r="19" ht="12" customHeight="1">
-      <c r="A19" s="68" t="n"/>
-      <c r="B19" s="95" t="n"/>
-      <c r="C19" s="95" t="n"/>
-      <c r="D19" s="137" t="n"/>
-      <c r="E19" s="128" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="95" t="n"/>
-      <c r="C20" s="95" t="n"/>
-      <c r="D20" s="137" t="n"/>
-      <c r="E20" s="128" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="95" t="n"/>
-      <c r="D21" s="137" t="n"/>
-      <c r="E21" s="128" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="112" t="n"/>
-      <c r="B22" s="113" t="n"/>
-      <c r="C22" s="95" t="n"/>
-      <c r="D22" s="137" t="n"/>
-      <c r="E22" s="128" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="112" t="n"/>
-      <c r="B23" s="113" t="n"/>
-      <c r="C23" s="95" t="n"/>
-      <c r="D23" s="137" t="n"/>
-      <c r="E23" s="128" t="n"/>
-    </row>
-    <row r="24" ht="12" customHeight="1" thickBot="1">
-      <c r="A24" s="51" t="n"/>
-      <c r="D24" s="137" t="n"/>
-      <c r="E24" s="128" t="n"/>
-    </row>
-    <row r="25" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prerequisite </t>
-        </is>
-      </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
-      <c r="D25" s="45" t="n"/>
-      <c r="E25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="94" t="n"/>
-      <c r="E26" s="43" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="94" t="n"/>
-      <c r="E27" s="43" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="94" t="n"/>
-      <c r="E28" s="43" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="94" t="n"/>
-      <c r="E29" s="43" t="n"/>
-    </row>
-    <row r="30" ht="12" customHeight="1" thickBot="1">
-      <c r="A30" s="51" t="n"/>
-      <c r="E30" s="43" t="n"/>
-    </row>
-    <row r="31" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A31" s="44" t="inlineStr">
-        <is>
-          <t>Key RICEF Objects</t>
-        </is>
-      </c>
-      <c r="B31" s="45" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="46" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="94" t="inlineStr">
-        <is>
-          <t>Master Data Validation</t>
-        </is>
-      </c>
-      <c r="E32" s="43" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="94" t="inlineStr">
-        <is>
-          <t>SAP PO Post and Validation</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="94" t="inlineStr">
-        <is>
-          <t>SAP Invoice to SAP</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="n"/>
-    </row>
-    <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="94" t="inlineStr">
-        <is>
-          <t>Payment Remitance Validation to Ariba</t>
-        </is>
-      </c>
-      <c r="E35" s="52" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="117" t="n"/>
-      <c r="C36" s="119" t="n"/>
-      <c r="E36" s="43" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="117" t="n"/>
-      <c r="C37" s="119" t="n"/>
-      <c r="E37" s="43" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1" thickBot="1">
-      <c r="A38" s="53" t="inlineStr">
-        <is>
-          <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="n"/>
-    </row>
-    <row r="39" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A39" s="54" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B39" s="55" t="inlineStr">
-        <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="C39" s="55" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D39" s="55" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="E39" s="46" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="109" t="n"/>
-      <c r="B40" s="110" t="n"/>
-      <c r="C40" s="110" t="n"/>
-      <c r="D40" s="110" t="n"/>
-      <c r="E40" s="58" t="n"/>
-    </row>
-    <row r="41" ht="12.6" customHeight="1" thickBot="1">
-      <c r="A41" s="59" t="n"/>
-      <c r="B41" s="60" t="n"/>
-      <c r="C41" s="60" t="n"/>
-      <c r="D41" s="60" t="n"/>
-      <c r="E41" s="61" t="n"/>
-    </row>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12" customHeight="1"/>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="62" t="n"/>
-      <c r="B47" s="63" t="n"/>
-      <c r="C47" s="63" t="n"/>
-      <c r="D47" s="63" t="n"/>
-    </row>
-    <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="62" t="n"/>
-      <c r="B48" s="63" t="n"/>
-      <c r="C48" s="63" t="n"/>
-      <c r="D48" s="63" t="n"/>
-    </row>
-    <row r="49" ht="13.2" customHeight="1">
-      <c r="A49" s="64" t="n"/>
-      <c r="B49" s="65" t="n"/>
-      <c r="C49" s="66" t="n"/>
-      <c r="D49" s="65" t="n"/>
-      <c r="E49" s="65" t="n"/>
-    </row>
-    <row r="50" ht="13.2" customHeight="1">
-      <c r="A50" s="63" t="n"/>
-      <c r="B50" s="63" t="n"/>
-      <c r="C50" s="63" t="n"/>
-      <c r="D50" s="63" t="n"/>
-    </row>
-    <row r="51" ht="13.2" customHeight="1">
-      <c r="A51" s="63" t="n"/>
-      <c r="B51" s="63" t="n"/>
-      <c r="C51" s="63" t="n"/>
-      <c r="D51" s="63" t="n"/>
-    </row>
-    <row r="52" ht="13.2" customHeight="1">
-      <c r="A52" s="63" t="n"/>
-      <c r="B52" s="63" t="n"/>
-      <c r="C52" s="63" t="n"/>
-      <c r="D52" s="63" t="n"/>
-    </row>
-    <row r="53" ht="13.2" customHeight="1">
-      <c r="A53" s="63" t="n"/>
-      <c r="B53" s="63" t="n"/>
-      <c r="C53" s="63" t="n"/>
-      <c r="D53" s="63" t="n"/>
-    </row>
-    <row r="54" ht="13.2" customHeight="1">
-      <c r="A54" s="63" t="n"/>
-      <c r="B54" s="63" t="n"/>
-      <c r="C54" s="63" t="n"/>
-      <c r="D54" s="63" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="62" t="n"/>
-      <c r="B55" s="63" t="n"/>
-      <c r="C55" s="63" t="n"/>
-      <c r="D55" s="63" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="62" t="n"/>
-      <c r="B56" s="63" t="n"/>
-      <c r="C56" s="63" t="n"/>
-      <c r="D56" s="63" t="n"/>
-    </row>
-    <row r="57" ht="13.2" customHeight="1">
-      <c r="A57" s="63" t="n"/>
-      <c r="B57" s="63" t="n"/>
-      <c r="C57" s="63" t="n"/>
-      <c r="D57" s="63" t="n"/>
-      <c r="E57" s="63" t="n"/>
-    </row>
-    <row r="58" ht="13.2" customHeight="1">
-      <c r="A58" s="63" t="n"/>
-      <c r="B58" s="63" t="n"/>
-      <c r="C58" s="63" t="n"/>
-      <c r="D58" s="63" t="n"/>
-      <c r="E58" s="63" t="n"/>
-    </row>
-    <row r="59" ht="13.2" customHeight="1">
-      <c r="A59" s="63" t="n"/>
-      <c r="B59" s="63" t="n"/>
-      <c r="C59" s="63" t="n"/>
-      <c r="D59" s="63" t="n"/>
-      <c r="E59" s="63" t="n"/>
-    </row>
-    <row r="60" ht="13.2" customHeight="1">
-      <c r="A60" s="63" t="n"/>
-      <c r="B60" s="63" t="n"/>
-      <c r="C60" s="63" t="n"/>
-      <c r="D60" s="63" t="n"/>
-      <c r="E60" s="63" t="n"/>
-    </row>
-    <row r="61" ht="13.2" customHeight="1">
-      <c r="A61" s="63" t="n"/>
-      <c r="B61" s="63" t="n"/>
-      <c r="C61" s="63" t="n"/>
-      <c r="D61" s="63" t="n"/>
-      <c r="E61" s="63" t="n"/>
-    </row>
-    <row r="62" ht="13.2" customHeight="1">
-      <c r="A62" s="63" t="n"/>
-      <c r="B62" s="63" t="n"/>
-      <c r="C62" s="63" t="n"/>
-      <c r="D62" s="63" t="n"/>
-      <c r="E62" s="63" t="n"/>
-    </row>
-    <row r="63" ht="13.2" customHeight="1">
-      <c r="A63" s="63" t="n"/>
-      <c r="B63" s="63" t="n"/>
-      <c r="C63" s="63" t="n"/>
-      <c r="D63" s="63" t="n"/>
-      <c r="E63" s="63" t="n"/>
-    </row>
-    <row r="64" ht="13.2" customHeight="1">
-      <c r="A64" s="63" t="n"/>
-      <c r="B64" s="63" t="n"/>
-      <c r="C64" s="63" t="n"/>
-      <c r="D64" s="63" t="n"/>
-      <c r="E64" s="63" t="n"/>
-    </row>
-    <row r="65" ht="13.2" customHeight="1">
-      <c r="A65" s="63" t="n"/>
-      <c r="B65" s="63" t="n"/>
-      <c r="C65" s="63" t="n"/>
-      <c r="D65" s="63" t="n"/>
-      <c r="E65" s="63" t="n"/>
-    </row>
-    <row r="66" ht="13.2" customHeight="1">
-      <c r="A66" s="63" t="n"/>
-      <c r="B66" s="63" t="n"/>
-      <c r="C66" s="63" t="n"/>
-      <c r="D66" s="63" t="n"/>
-      <c r="E66" s="63" t="n"/>
-    </row>
-    <row r="67" ht="13.2" customHeight="1">
-      <c r="A67" s="63" t="n"/>
-      <c r="B67" s="63" t="n"/>
-      <c r="C67" s="63" t="n"/>
-      <c r="D67" s="63" t="n"/>
-      <c r="E67" s="63" t="n"/>
-    </row>
-    <row r="68" ht="13.2" customHeight="1">
-      <c r="A68" s="63" t="n"/>
-      <c r="B68" s="63" t="n"/>
-      <c r="C68" s="63" t="n"/>
-      <c r="D68" s="63" t="n"/>
-      <c r="E68" s="63" t="n"/>
-    </row>
-    <row r="69" ht="13.2" customHeight="1">
-      <c r="A69" s="63" t="n"/>
-      <c r="B69" s="63" t="n"/>
-      <c r="C69" s="63" t="n"/>
-      <c r="D69" s="63" t="n"/>
-      <c r="E69" s="63" t="n"/>
-    </row>
-    <row r="70" ht="13.2" customHeight="1">
-      <c r="A70" s="63" t="n"/>
-      <c r="B70" s="63" t="n"/>
-      <c r="C70" s="63" t="n"/>
-      <c r="D70" s="63" t="n"/>
-      <c r="E70" s="63" t="n"/>
+    <row r="1" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41"/>
+    </row>
+    <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="98" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="100"/>
+    </row>
+    <row r="4" spans="1:6" ht="12" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="100"/>
+    </row>
+    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="103"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="102"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="105"/>
+    </row>
+    <row r="7" spans="1:6" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="E7" s="43"/>
+    </row>
+    <row r="8" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="108"/>
+    </row>
+    <row r="9" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="112"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="112"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114"/>
+    </row>
+    <row r="12" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="112"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="112"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="114"/>
+    </row>
+    <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="112"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="114"/>
+    </row>
+    <row r="15" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="112"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="114"/>
+    </row>
+    <row r="16" spans="1:6" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="46"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="69"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="116"/>
+    </row>
+    <row r="18" spans="1:5" ht="12" x14ac:dyDescent="0.25">
+      <c r="A18" s="67"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="118"/>
+    </row>
+    <row r="19" spans="1:5" ht="12" x14ac:dyDescent="0.25">
+      <c r="A19" s="68"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="118"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="118"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="50"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="118"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="118"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="118"/>
+    </row>
+    <row r="24" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="51"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="118"/>
+    </row>
+    <row r="25" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="46"/>
+    </row>
+    <row r="26" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="94"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="94"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="43"/>
+    </row>
+    <row r="30" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
+      <c r="E30" s="43"/>
+    </row>
+    <row r="31" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="46"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="43"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="95"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="43"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="95"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="43"/>
+    </row>
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="95"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="52"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="117"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="43"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="117"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="43"/>
+    </row>
+    <row r="38" spans="1:5" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="43"/>
+    </row>
+    <row r="39" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="46"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="56"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
+    </row>
+    <row r="41" spans="1:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="59"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
+    </row>
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="62"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+    </row>
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="62"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+    </row>
+    <row r="49" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A49" s="64"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="65"/>
+    </row>
+    <row r="50" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A50" s="63"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+    </row>
+    <row r="51" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A51" s="63"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+    </row>
+    <row r="52" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A52" s="63"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+    </row>
+    <row r="53" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A53" s="63"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+    </row>
+    <row r="54" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A54" s="63"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+    </row>
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="62"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+    </row>
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="62"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+    </row>
+    <row r="57" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" s="63"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+    </row>
+    <row r="58" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A58" s="63"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+    </row>
+    <row r="59" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A59" s="63"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+    </row>
+    <row r="60" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A60" s="63"/>
+      <c r="B60" s="63"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+    </row>
+    <row r="61" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A61" s="63"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+    </row>
+    <row r="62" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A62" s="63"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+    </row>
+    <row r="63" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A63" s="63"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+    </row>
+    <row r="64" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A64" s="63"/>
+      <c r="B64" s="63"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+    </row>
+    <row r="65" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A65" s="63"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+    </row>
+    <row r="66" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A66" s="63"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+    </row>
+    <row r="67" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A67" s="63"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+    </row>
+    <row r="68" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A68" s="63"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+    </row>
+    <row r="69" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A69" s="63"/>
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+    </row>
+    <row r="70" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A70" s="63"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="63"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:E6"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A9:E15"/>
     <mergeCell ref="D17:E24"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B5:E6"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D2:E2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E2">
       <formula1>"R4-Cycle 1,R4-Cycle 2,R4-Cycle 3,R4-Cycle 4,R4-Regression Test,R4-Business Simulation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" scale="69"/>
+  <pageSetup scale="69" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="35.6640625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="35.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10.33203125" customWidth="1" style="86" min="1" max="1"/>
-    <col width="18.6640625" customWidth="1" style="86" min="2" max="2"/>
-    <col width="10.33203125" customWidth="1" style="72" min="3" max="3"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" style="72" min="4" max="4"/>
-    <col width="14" customWidth="1" style="86" min="5" max="5"/>
-    <col width="80.44140625" customWidth="1" style="87" min="6" max="6"/>
-    <col width="62.44140625" customWidth="1" style="72" min="7" max="7"/>
-    <col width="46.44140625" customWidth="1" style="72" min="8" max="8"/>
-    <col width="15.88671875" customWidth="1" style="72" min="9" max="9"/>
-    <col width="41.33203125" customWidth="1" style="72" min="10" max="10"/>
-    <col width="18.88671875" customWidth="1" style="86" min="11" max="11"/>
-    <col width="18.6640625" customWidth="1" style="72" min="12" max="12"/>
-    <col width="17.44140625" customWidth="1" style="72" min="13" max="13"/>
-    <col width="16.44140625" customWidth="1" style="87" min="14" max="14"/>
-    <col width="13.33203125" customWidth="1" style="87" min="15" max="15"/>
-    <col width="37.109375" bestFit="1" customWidth="1" style="72" min="16" max="16"/>
-    <col width="9.109375" customWidth="1" style="72" min="17" max="17"/>
-    <col width="35.6640625" customWidth="1" style="72" min="18" max="16384"/>
+    <col min="1" max="1" width="10.33203125" style="86" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="86" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="72" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="72" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="86" customWidth="1"/>
+    <col min="6" max="6" width="80.44140625" style="87" customWidth="1"/>
+    <col min="7" max="7" width="62.44140625" style="72" customWidth="1"/>
+    <col min="8" max="8" width="46.44140625" style="72" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" style="72" customWidth="1"/>
+    <col min="10" max="10" width="41.33203125" style="72" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" style="86" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" style="72" customWidth="1"/>
+    <col min="13" max="13" width="17.44140625" style="72" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="87" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" style="87" customWidth="1"/>
+    <col min="16" max="16" width="37.109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" style="72"/>
+    <col min="18" max="16384" width="35.6640625" style="72"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="120" t="inlineStr">
-        <is>
-          <t>Scenario Number</t>
-        </is>
-      </c>
-      <c r="B1" s="120" t="n"/>
-      <c r="C1" s="120" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D1" s="120" t="n"/>
-      <c r="E1" s="120" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="F1" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Description </t>
-        </is>
-      </c>
-      <c r="G1" s="120" t="inlineStr">
-        <is>
-          <t>Test Data / Test Execution</t>
-        </is>
-      </c>
-      <c r="H1" s="120" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="I1" s="121" t="inlineStr">
-        <is>
-          <t>Step Completed
-Sucessfullyåç</t>
-        </is>
-      </c>
-      <c r="J1" s="120" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="K1" s="120" t="inlineStr">
-        <is>
-          <t>FI Impact</t>
-        </is>
-      </c>
-      <c r="L1" s="120" t="inlineStr">
-        <is>
-          <t>RICEF Tested</t>
-        </is>
-      </c>
-      <c r="M1" s="120" t="inlineStr">
-        <is>
-          <t>TPR #</t>
-        </is>
-      </c>
-      <c r="N1" s="120" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="O1" s="122" t="inlineStr">
-        <is>
-          <t>Tester/User ID</t>
-        </is>
-      </c>
-      <c r="P1" s="120" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="139" t="n"/>
-      <c r="B2" s="120" t="n"/>
-      <c r="C2" s="139" t="n"/>
-      <c r="D2" s="73" t="n"/>
-      <c r="E2" s="139" t="n"/>
-      <c r="F2" s="139" t="n"/>
-      <c r="G2" s="139" t="n"/>
-      <c r="H2" s="139" t="n"/>
-      <c r="I2" s="140" t="n"/>
-      <c r="J2" s="139" t="n"/>
-      <c r="K2" s="73" t="inlineStr">
-        <is>
-          <t>Y or N</t>
-        </is>
-      </c>
-      <c r="L2" s="139" t="n"/>
-      <c r="M2" s="139" t="n"/>
-      <c r="N2" s="139" t="n"/>
-      <c r="O2" s="141" t="n"/>
-      <c r="P2" s="139" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="74" t="n"/>
-      <c r="B3" s="74" t="inlineStr">
-        <is>
-          <t>Scenario No.</t>
-        </is>
-      </c>
-      <c r="C3" s="74" t="n"/>
-      <c r="D3" s="74" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="E3" s="74" t="n"/>
-      <c r="F3" s="75" t="n"/>
-      <c r="G3" s="76" t="n"/>
-      <c r="H3" s="76" t="n"/>
-      <c r="I3" s="76" t="n"/>
-      <c r="J3" s="74" t="n"/>
-      <c r="K3" s="74" t="n"/>
-      <c r="L3" s="74" t="n"/>
-      <c r="M3" s="74" t="n"/>
-      <c r="N3" s="77" t="n"/>
-      <c r="O3" s="77" t="n"/>
-      <c r="P3" s="74" t="n"/>
-    </row>
-    <row r="4" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A4" s="70" t="inlineStr">
-        <is>
-          <t>BL_001</t>
-        </is>
-      </c>
-      <c r="B4" s="70" t="inlineStr">
-        <is>
-          <t>GPO-001</t>
-        </is>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="120" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="71"/>
+      <c r="E1" s="120" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="120"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="120"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="74"/>
+    </row>
+    <row r="4" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A4" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="70">
-        <f>ROW(A4)-3</f>
-        <v/>
-      </c>
-      <c r="D4" s="70" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="E4" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F4" s="70" t="inlineStr">
-        <is>
-          <t>Complete script GEN-002 to log into Ariba "Advanced" Buying and Invoicing.</t>
-        </is>
-      </c>
-      <c r="G4" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Login
-Password
-</t>
-        </is>
-      </c>
-      <c r="H4" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nexus Water Group homepage is presented. </t>
-        </is>
+        <f t="shared" ref="C4:C9" si="0">ROW(A4)-3</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="79" t="s">
+        <v>83</v>
       </c>
       <c r="I4" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J4" s="70" t="n"/>
-      <c r="K4" s="70" t="n"/>
-      <c r="L4" s="70" t="n"/>
-      <c r="M4" s="70" t="n"/>
-      <c r="N4" s="70" t="n"/>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="70" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="81">
-      <c r="A5" s="70" t="n"/>
-      <c r="B5" s="70" t="n"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+    </row>
+    <row r="5" spans="1:16" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="70"/>
+      <c r="B5" s="70"/>
       <c r="C5" s="70">
-        <f>ROW(A5)-3</f>
-        <v/>
-      </c>
-      <c r="D5" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E5" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F5" s="89" t="inlineStr">
-        <is>
-          <t>Click on Catalog Tab</t>
-        </is>
-      </c>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="70" t="inlineStr">
-        <is>
-          <t>Catalog page is displayed</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="78"/>
+      <c r="H5" s="70" t="s">
+        <v>85</v>
       </c>
       <c r="I5" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="70" t="n"/>
-      <c r="K5" s="70" t="n"/>
-      <c r="L5" s="70" t="n"/>
-      <c r="M5" s="70" t="n"/>
-      <c r="N5" s="70" t="n"/>
-      <c r="O5" s="70" t="n"/>
-      <c r="P5" s="70" t="n"/>
-    </row>
-    <row r="6" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A6" s="70" t="n"/>
-      <c r="B6" s="70" t="n"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+    </row>
+    <row r="6" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A6" s="70"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="70">
-        <f>ROW(A6)-3</f>
-        <v/>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>On the search bar where it says "Search by part #, supplier name or keyword", type in the item you want to purchase.</t>
-        </is>
-      </c>
-      <c r="G6" s="78" t="inlineStr">
-        <is>
-          <t>Power Pen! Reading Comprehension Quiz Cards - Gr. 1</t>
-        </is>
-      </c>
-      <c r="H6" s="70" t="n"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="70"/>
       <c r="I6" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="70" t="n"/>
-      <c r="K6" s="70" t="n"/>
-      <c r="L6" s="70" t="n"/>
-      <c r="M6" s="70" t="n"/>
-      <c r="N6" s="70" t="n"/>
-      <c r="O6" s="70" t="n"/>
-      <c r="P6" s="70" t="n"/>
-    </row>
-    <row r="7" ht="39.75" customFormat="1" customHeight="1" s="81">
-      <c r="A7" s="70" t="n"/>
-      <c r="B7" s="70" t="n"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+    </row>
+    <row r="7" spans="1:16" s="81" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="70"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="70">
-        <f>ROW(A7)-3</f>
-        <v/>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E7" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F7" s="70" t="inlineStr">
-        <is>
-          <t>From the search result, find the item. Enter the desired quantity  in the "Qty" box.</t>
-        </is>
-      </c>
-      <c r="G7" s="78" t="inlineStr">
-        <is>
-          <t>Quantity: 12</t>
-        </is>
-      </c>
-      <c r="H7" s="70" t="inlineStr">
-        <is>
-          <t>Desired quantity is indicated.</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="78" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>45</v>
       </c>
       <c r="I7" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="70" t="n"/>
-      <c r="K7" s="70" t="n"/>
-      <c r="L7" s="70" t="n"/>
-      <c r="M7" s="70" t="n"/>
-      <c r="N7" s="70" t="n"/>
-      <c r="O7" s="70" t="n"/>
-      <c r="P7" s="70" t="n"/>
-    </row>
-    <row r="8" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A8" s="70" t="n"/>
-      <c r="B8" s="70" t="n"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+    </row>
+    <row r="8" spans="1:16" s="81" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="70"/>
+      <c r="B8" s="70"/>
       <c r="C8" s="70">
-        <f>ROW(A8)-3</f>
-        <v/>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E8" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F8" s="70" t="inlineStr">
-        <is>
-          <t>Press "Add to Cart" button.</t>
-        </is>
-      </c>
-      <c r="G8" s="70" t="n"/>
-      <c r="H8" s="70" t="inlineStr">
-        <is>
-          <t>Shopping Cart popup  window appears.</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70" t="s">
+        <v>47</v>
       </c>
       <c r="I8" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="70" t="n"/>
-      <c r="K8" s="70" t="n"/>
-      <c r="L8" s="70" t="n"/>
-      <c r="M8" s="70" t="n"/>
-      <c r="N8" s="70" t="n"/>
-      <c r="O8" s="70" t="n"/>
-      <c r="P8" s="70" t="n"/>
-    </row>
-    <row r="9" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A9" s="70" t="n"/>
-      <c r="B9" s="70" t="n"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+    </row>
+    <row r="9" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="70">
-        <f>ROW(A9)-3</f>
-        <v/>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E9" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F9" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen. Click on Proceed to Checkout button.
-</t>
-        </is>
-      </c>
-      <c r="G9" s="88" t="inlineStr">
-        <is>
-          <t>
-</t>
-        </is>
-      </c>
-      <c r="H9" s="82" t="inlineStr">
-        <is>
-          <t>Requisition screen appears. The system assigns the PR number to the document.</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="82" t="s">
+        <v>49</v>
       </c>
       <c r="I9" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="70" t="n"/>
-      <c r="K9" s="70" t="n"/>
-      <c r="L9" s="70" t="n"/>
-      <c r="M9" s="70" t="n"/>
-      <c r="N9" s="70" t="n"/>
-      <c r="O9" s="70" t="n"/>
-      <c r="P9" s="70" t="n"/>
-    </row>
-    <row r="10" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A10" s="70" t="n"/>
-      <c r="B10" s="70" t="n"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+    </row>
+    <row r="10" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
       <c r="C10" s="70">
-        <f>ROW(A10)-3</f>
-        <v/>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header</t>
-        </is>
-      </c>
-      <c r="E10" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F10" s="83" t="inlineStr">
-        <is>
-          <t>Enter the requistion title on "Requistion title" box.</t>
-        </is>
-      </c>
-      <c r="G10" s="78" t="inlineStr">
-        <is>
-          <t>AT-23</t>
-        </is>
-      </c>
-      <c r="H10" s="70" t="inlineStr">
-        <is>
-          <t>Requisition title is updated.</t>
-        </is>
+        <f t="shared" ref="C10:C17" si="1">ROW(A10)-3</f>
+        <v>7</v>
+      </c>
+      <c r="D10" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="70" t="s">
+        <v>52</v>
       </c>
       <c r="I10" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="70" t="n"/>
-      <c r="K10" s="70" t="n"/>
-      <c r="L10" s="70" t="n"/>
-      <c r="M10" s="70" t="n"/>
-      <c r="N10" s="70" t="n"/>
-      <c r="O10" s="70" t="n"/>
-      <c r="P10" s="70" t="n"/>
-    </row>
-    <row r="11" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A11" s="70" t="n"/>
-      <c r="B11" s="70" t="n"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+    </row>
+    <row r="11" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
       <c r="C11" s="70">
-        <f>ROW(A11)-3</f>
-        <v/>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header</t>
-        </is>
-      </c>
-      <c r="E11" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F11" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enter or verify the remaing data elements on the Requistion screen.
-Note: Only "red " items should be editable.
-</t>
-        </is>
-      </c>
-      <c r="G11" s="90" t="n"/>
-      <c r="H11" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated without any error.</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="90"/>
+      <c r="H11" s="70" t="s">
+        <v>54</v>
       </c>
       <c r="I11" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>Need-by is Today +5</t>
-        </is>
-      </c>
-      <c r="K11" s="70" t="n"/>
-      <c r="L11" s="70" t="n"/>
-      <c r="M11" s="70" t="n"/>
-      <c r="N11" s="70" t="n"/>
-      <c r="O11" s="70" t="n"/>
-      <c r="P11" s="70" t="n"/>
-    </row>
-    <row r="12" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A12" s="70" t="n"/>
-      <c r="B12" s="70" t="n"/>
+      <c r="J11" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+    </row>
+    <row r="12" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
       <c r="C12" s="70">
-        <f>ROW(A12)-3</f>
-        <v/>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E12" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F12" s="91" t="inlineStr">
-        <is>
-          <t>Click on the checkbox in the line for the item (towards the item lines' top left).
-Click on Actions dropdown and then Edit Details.</t>
-        </is>
-      </c>
-      <c r="G12" s="92" t="n"/>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>Edit Detail page for the item is displayed.</t>
-        </is>
-      </c>
-      <c r="I12" s="80" t="n"/>
-      <c r="J12" s="70" t="n"/>
-      <c r="K12" s="70" t="n"/>
-      <c r="L12" s="70" t="n"/>
-      <c r="M12" s="70" t="n"/>
-      <c r="N12" s="70" t="n"/>
-      <c r="O12" s="70" t="n"/>
-      <c r="P12" s="70" t="n"/>
-    </row>
-    <row r="13" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A13" s="70" t="n"/>
-      <c r="B13" s="70" t="n"/>
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="91" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="92"/>
+      <c r="H12" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="80"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+    </row>
+    <row r="13" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
       <c r="C13" s="70">
-        <f>ROW(A13)-3</f>
-        <v/>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E13" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F13" s="91" t="inlineStr">
-        <is>
-          <t>Enter or verify the Line Item Details for the item.
-(Most details in this section is set to default)</t>
-        </is>
-      </c>
-      <c r="G13" s="92" t="inlineStr">
-        <is>
-          <t>No.: 1
-Full Description: Power Pen! Reading Comprehension Quiz Cards - Gr. 1
-Supplier Part Number: BD581
-Supplier Part Auxiliary ID: 
-Qty: 12
-UOM: each
-Price: $15.99 USD
-Price Unit Quantity: 1
-Unit Conversion: 
-Pricing Description: 
-Discount: 
-Net Amount: $191.88 USD Fx
-Charges: 
-Taxes: 
-Amount: $191.88 USD
-Commodity Code: Developmental and professional teaching aids and materials and accessories and supplies
-Supplier: LAKESHORE LEARNING MATERIALS
-Contact: LAKESHORE LEARNING MATERIALS [ select ]
-Service Item: No
-Contract: [ select ]</t>
-        </is>
-      </c>
-      <c r="H13" s="90" t="inlineStr">
-        <is>
-          <t>Fields are validated and updated if necessary.</t>
-        </is>
-      </c>
-      <c r="I13" s="80" t="n"/>
-      <c r="J13" s="70" t="n"/>
-      <c r="K13" s="70" t="n"/>
-      <c r="L13" s="70" t="n"/>
-      <c r="M13" s="70" t="n"/>
-      <c r="N13" s="70" t="n"/>
-      <c r="O13" s="70" t="n"/>
-      <c r="P13" s="70" t="n"/>
-    </row>
-    <row r="14" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A14" s="70" t="n"/>
-      <c r="B14" s="70" t="n"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="92"/>
+      <c r="H13" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="80"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+    </row>
+    <row r="14" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
       <c r="C14" s="70">
-        <f>ROW(A14)-3</f>
-        <v/>
-      </c>
-      <c r="D14" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E14" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F14" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scroll down to Accounting - by Line Item Section
-Enter or  verify the information in the Accounting  section. </t>
-        </is>
-      </c>
-      <c r="G14" s="91" t="inlineStr">
-        <is>
-          <t>Account Type: Expense
-Bill To: Ariba - Pittsburgh
-Cost Center: Ariba - Office of the CEO
-Business Unit: Ariba - Marketing
-Company: Ariba - Company 1
-Account: ARIBA - Expense Account 1
-Project: (no value)</t>
-        </is>
-      </c>
-      <c r="H14" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D14" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="93" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="91"/>
+      <c r="H14" s="70" t="s">
+        <v>57</v>
       </c>
       <c r="I14" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="70" t="n"/>
-      <c r="K14" s="70" t="n"/>
-      <c r="L14" s="70" t="n"/>
-      <c r="M14" s="70" t="n"/>
-      <c r="N14" s="70" t="n"/>
-      <c r="O14" s="70" t="n"/>
-      <c r="P14" s="70" t="n"/>
-    </row>
-    <row r="15" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A15" s="70" t="n"/>
-      <c r="B15" s="70" t="n"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+    </row>
+    <row r="15" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A15" s="70"/>
+      <c r="B15" s="70"/>
       <c r="C15" s="70">
-        <f>ROW(A15)-3</f>
-        <v/>
-      </c>
-      <c r="D15" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E15" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F15" s="90" t="inlineStr">
-        <is>
-          <t>Enter or  verify the information in the Shipping - by Line Item section.</t>
-        </is>
-      </c>
-      <c r="G15" s="90" t="inlineStr">
-        <is>
-          <t>Ship_To: Ariba - Pittsburgh
-Deliver_To: Samit Paudel
-Need-by_Date: Tue, 29 Apr, 2025</t>
-        </is>
-      </c>
-      <c r="H15" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="90"/>
+      <c r="H15" s="70" t="s">
+        <v>57</v>
       </c>
       <c r="I15" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="70" t="n"/>
-      <c r="K15" s="70" t="n"/>
-      <c r="L15" s="70" t="n"/>
-      <c r="M15" s="70" t="n"/>
-      <c r="N15" s="70" t="n"/>
-      <c r="O15" s="70" t="n"/>
-      <c r="P15" s="70" t="n"/>
-    </row>
-    <row r="16" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A16" s="70" t="n"/>
-      <c r="B16" s="70" t="n"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+    </row>
+    <row r="16" spans="1:16" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.35">
+      <c r="A16" s="70"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="70">
-        <f>ROW(A16)-3</f>
-        <v/>
-      </c>
-      <c r="D16" s="70" t="inlineStr">
-        <is>
-          <t>Requisition</t>
-        </is>
-      </c>
-      <c r="E16" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F16" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Press "Submit"  to submit the requisition for approval. </t>
-        </is>
-      </c>
-      <c r="G16" s="85" t="n"/>
-      <c r="H16" s="85" t="inlineStr">
-        <is>
-          <t>Message appears "Your requisition has been sent for approval.</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="D16" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85" t="s">
+        <v>60</v>
       </c>
       <c r="I16" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="70" t="n"/>
-      <c r="K16" s="70" t="n"/>
-      <c r="L16" s="70" t="n"/>
-      <c r="M16" s="70" t="n"/>
-      <c r="N16" s="70" t="n"/>
-      <c r="O16" s="70" t="n"/>
-      <c r="P16" s="70" t="n"/>
-    </row>
-    <row r="17" ht="54" customFormat="1" customHeight="1" s="81">
-      <c r="A17" s="70" t="n"/>
-      <c r="B17" s="70" t="n"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+    </row>
+    <row r="17" spans="1:16" s="81" customFormat="1" ht="54" x14ac:dyDescent="0.4">
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="70">
-        <f>ROW(A17)-3</f>
-        <v/>
-      </c>
-      <c r="D17" s="70" t="inlineStr">
-        <is>
-          <t>View Approval Flow</t>
-        </is>
-      </c>
-      <c r="E17" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F17" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Click on View Requisition to display the created requisiton. </t>
-        </is>
-      </c>
-      <c r="G17" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Submitted</t>
-        </is>
-      </c>
-      <c r="H17" s="82" t="inlineStr">
-        <is>
-          <t>The PR is now on Submitted status.
-Approval Flow is now active shown by green flow.</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="82" t="s">
+        <v>64</v>
       </c>
       <c r="I17" s="80" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="70" t="n"/>
-      <c r="K17" s="70" t="n"/>
-      <c r="L17" s="70" t="n"/>
-      <c r="M17" s="70" t="n"/>
-      <c r="N17" s="70" t="n"/>
-      <c r="O17" s="70" t="n"/>
-      <c r="P17" s="70" t="n"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="P1:P2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="N4:N17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4:N17">
       <formula1>"10 - Not Started,20 - In-Process,30 - TPR Hold,40 - DEV Hold,50 - Pass,60 - N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="K4:K17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K17">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E17">
       <formula1>"AP,Buyer,PO Approv,Inv Approv,Watcher,SAP Tech Team,Prem Tech,Prem Funct"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" scale="61" fitToHeight="10" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="61" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A3:R46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:R46"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="14.88671875" customWidth="1" style="2" min="1" max="1"/>
-    <col width="8.44140625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="14.33203125" customWidth="1" style="2" min="3" max="7"/>
-    <col width="14.33203125" customWidth="1" style="1" min="8" max="9"/>
-    <col width="11.6640625" customWidth="1" style="1" min="10" max="11"/>
-    <col width="14.33203125" bestFit="1" customWidth="1" style="1" min="12" max="17"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="1" min="18" max="18"/>
-    <col width="9.109375" customWidth="1" style="1" min="19" max="16384"/>
+    <col min="1" max="1" width="14.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="2" customWidth="1"/>
+    <col min="3" max="7" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="11.6640625" style="1" customWidth="1"/>
+    <col min="12" max="17" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="17.25" customHeight="1" thickBot="1"/>
-    <row r="3" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Count of Status</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="21" t="n"/>
-    </row>
-    <row r="4" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Scenario Number</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>10 - Not Started</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>20 - In-Process</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>30 - TPR Hold</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
-        <is>
-          <t>40 - DEV Hold</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>50 - Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>60 - N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="13.2" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>PP_018</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>RTR</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="4" t="n">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+    </row>
+    <row r="4" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+    </row>
+    <row r="5" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="6" t="n">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" ht="13.2" customHeight="1">
-      <c r="A6" s="26" t="n"/>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>PTP</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="27" t="n">
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+    </row>
+    <row r="6" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>8</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="27">
         <v>2</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="28">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" ht="13.2" customHeight="1">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n">
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+    </row>
+    <row r="7" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27">
         <v>25</v>
       </c>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="28" t="n">
+      <c r="I7" s="27"/>
+      <c r="J7" s="28">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>IMWM</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n">
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+    </row>
+    <row r="8" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
         <v>5</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="28">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>PP_018 Total</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n">
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+    </row>
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10">
         <v>2</v>
       </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n">
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10">
         <v>38</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="10">
         <v>6</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="11">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>ZZZ999</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="10" t="n">
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+    </row>
+    <row r="10" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10">
         <v>1</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="10">
         <v>1</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="10">
         <v>1</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="10">
         <v>1</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="11">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>ZZZ999 Total</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="4" t="n">
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4">
         <v>1</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="4">
         <v>1</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="10" t="n">
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+    </row>
+    <row r="12" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10">
         <v>3</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="10">
         <v>1</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="10">
         <v>1</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="10">
         <v>1</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="10">
         <v>39</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="10">
         <v>7</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="11">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1"/>
-    <row r="14" ht="17.25" customHeight="1"/>
-    <row r="15" ht="17.25" customHeight="1"/>
-    <row r="16" ht="17.25" customHeight="1"/>
-    <row r="17" ht="17.25" customHeight="1"/>
-    <row r="18" ht="17.25" customHeight="1"/>
-    <row r="19" ht="17.25" customHeight="1"/>
-    <row r="20" ht="17.25" customHeight="1"/>
-    <row r="21" ht="17.25" customHeight="1"/>
-    <row r="22" ht="17.25" customHeight="1"/>
-    <row r="23" ht="17.25" customHeight="1"/>
-    <row r="24" ht="17.25" customHeight="1"/>
-    <row r="25" ht="17.25" customHeight="1"/>
-    <row r="26" ht="17.25" customHeight="1"/>
-    <row r="27" ht="17.25" customHeight="1"/>
-    <row r="28" ht="17.25" customHeight="1"/>
-    <row r="29" ht="17.25" customHeight="1"/>
-    <row r="30" ht="17.25" customHeight="1"/>
-    <row r="31" ht="17.25" customHeight="1"/>
-    <row r="32" ht="17.25" customHeight="1"/>
-    <row r="33" ht="17.25" customHeight="1"/>
-    <row r="34" ht="17.25" customHeight="1"/>
-    <row r="35" ht="17.25" customHeight="1"/>
-    <row r="36" ht="17.25" customHeight="1"/>
-    <row r="37" ht="17.25" customHeight="1"/>
-    <row r="38" ht="17.25" customHeight="1"/>
-    <row r="39" ht="17.25" customHeight="1"/>
-    <row r="40" ht="17.25" customHeight="1"/>
-    <row r="41" ht="17.25" customHeight="1"/>
-    <row r="42" ht="17.25" customHeight="1"/>
-    <row r="43" ht="17.25" customHeight="1"/>
-    <row r="44" ht="17.25" customHeight="1"/>
-    <row r="45" ht="17.25" customHeight="1"/>
-    <row r="46" ht="17.25" customHeight="1"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+    </row>
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+    </row>
+    <row r="17" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+    </row>
+    <row r="18" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+    </row>
+    <row r="19" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+    </row>
+    <row r="20" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+    </row>
+    <row r="21" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+    </row>
+    <row r="22" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+    </row>
+    <row r="23" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+    </row>
+    <row r="24" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+    </row>
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+    </row>
+    <row r="26" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+    </row>
+    <row r="27" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+    </row>
+    <row r="28" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+    </row>
+    <row r="29" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+    </row>
+    <row r="30" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+    </row>
+    <row r="31" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+    </row>
+    <row r="38" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+    </row>
+    <row r="39" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+    </row>
+    <row r="40" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+    </row>
+    <row r="41" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+    </row>
+    <row r="42" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+    </row>
+    <row r="43" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+    </row>
+    <row r="44" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+    </row>
+    <row r="45" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+    </row>
+    <row r="46" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010019714232D8671D41B688C3A48C5AE621" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d53d216ca0852b3df112c80684e44a04">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0590885-0391-4acc-a1a2-62bdd649afdc" xmlns:ns3="f203ef26-be28-437c-ae01-5f41441de6d3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a994f462a7971573747b1ee30b6f4c90" ns2:_="" ns3:_="">
+    <xsd:import namespace="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
+    <xsd:import namespace="f203ef26-be28-437c-ae01-5f41441de6d3"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0590885-0391-4acc-a1a2-62bdd649afdc" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2cfdae59-7532-4cc8-8ce8-63e07576e745" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f203ef26-be28-437c-ae01-5f41441de6d3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{af0a4373-ad75-4169-a61b-b6de68ac2aea}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f203ef26-be28-437c-ae01-5f41441de6d3">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="f203ef26-be28-437c-ae01-5f41441de6d3">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="f203ef26-be28-437c-ae01-5f41441de6d3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0590885-0391-4acc-a1a2-62bdd649afdc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C2D16A-6A14-4FCF-9B7F-81D5BCF9F508}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B1B1D8-E7B0-43D3-BF30-A53ECE29C72F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
+    <ds:schemaRef ds:uri="f203ef26-be28-437c-ae01-5f41441de6d3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56BCB5A8-855F-4A49-B3E4-B6B1DAD57931}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E58E092-0497-4CF3-8876-CC340FCDDFD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f203ef26-be28-437c-ae01-5f41441de6d3"/>
+    <ds:schemaRef ds:uri="c0590885-0391-4acc-a1a2-62bdd649afdc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>